--- a/LMI Base.xlsx
+++ b/LMI Base.xlsx
@@ -8,78 +8,79 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7490922F-E1CC-473F-8F29-F6118EB781DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D61601FE-001E-4874-AA52-8337C6468984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro Liga" sheetId="1" r:id="rId1"/>
-    <sheet name="ChampionsLeague" sheetId="2" r:id="rId2"/>
-    <sheet name="CopaEstelar" sheetId="3" r:id="rId3"/>
-    <sheet name="Registro Champions" sheetId="4" r:id="rId4"/>
-    <sheet name="RegistroEstelar" sheetId="5" r:id="rId5"/>
-    <sheet name="BD" sheetId="6" r:id="rId6"/>
-    <sheet name="Lista" sheetId="7" r:id="rId7"/>
-    <sheet name="Clubes" sheetId="8" r:id="rId8"/>
-    <sheet name="Mercado" sheetId="9" r:id="rId9"/>
-    <sheet name="Campeones" sheetId="10" r:id="rId10"/>
-    <sheet name="RESPALDO" sheetId="11" r:id="rId11"/>
+    <sheet name="Renovaciones" sheetId="12" r:id="rId2"/>
+    <sheet name="ChampionsLeague" sheetId="2" r:id="rId3"/>
+    <sheet name="CopaEstelar" sheetId="3" r:id="rId4"/>
+    <sheet name="Registro Champions" sheetId="4" r:id="rId5"/>
+    <sheet name="RegistroEstelar" sheetId="5" r:id="rId6"/>
+    <sheet name="BD" sheetId="6" r:id="rId7"/>
+    <sheet name="Lista" sheetId="7" r:id="rId8"/>
+    <sheet name="Clubes" sheetId="8" r:id="rId9"/>
+    <sheet name="Mercado" sheetId="9" r:id="rId10"/>
+    <sheet name="Campeones" sheetId="10" r:id="rId11"/>
+    <sheet name="RESPALDO" sheetId="11" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Clubes!$A$1:$H$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Mercado!$A$1:$G$51</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Registro Champions'!$A$1:$D$122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Clubes!$A$1:$H$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">Mercado!$A$1:$G$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Registro Champions'!$A$1:$D$122</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Registro Liga'!$A$1:$D$251</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">RegistroEstelar!$A$1:$D$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">RegistroEstelar!$A$1:$D$80</definedName>
     <definedName name="AC_Milan">BD!$D$2:$D$24</definedName>
     <definedName name="AC_Milán">Lista!$E$2:$E$1048576</definedName>
     <definedName name="AcMilan">Lista!$E$2:$E$1048576</definedName>
-    <definedName name="Arsenal" localSheetId="5">BD!$J$2:$J$24</definedName>
+    <definedName name="Arsenal" localSheetId="6">BD!$J$2:$J$24</definedName>
     <definedName name="Arsenal">Lista!$K$2:$K$1048576</definedName>
     <definedName name="AstonVilla">Lista!$I$2:$I$1048576</definedName>
     <definedName name="Bayer_Munich">Lista!$O$2:$O$1048576</definedName>
-    <definedName name="Bayern_Leverkusen" localSheetId="5">BD!$E$2:$E$24</definedName>
+    <definedName name="Bayern_Leverkusen" localSheetId="6">BD!$E$2:$E$24</definedName>
     <definedName name="Bayern_Leverkusen">Lista!$F$2:$F$1048576</definedName>
     <definedName name="Bayern_Munich">BD!$N$2:$N$24</definedName>
-    <definedName name="Boca_Juniors" localSheetId="5">BD!$G$2:$G$24</definedName>
+    <definedName name="Boca_Juniors" localSheetId="6">BD!$G$2:$G$24</definedName>
     <definedName name="Boca_Juniors">Lista!$H$2:$H$1048576</definedName>
     <definedName name="BocaJuniors">Lista!$H$2:$H$1048576</definedName>
-    <definedName name="Como_1907" localSheetId="5">BD!$K$2:$K$24</definedName>
+    <definedName name="Como_1907" localSheetId="6">BD!$K$2:$K$24</definedName>
     <definedName name="COMO_1907">Lista!$L$2:$L$1048576</definedName>
     <definedName name="Como1907">Lista!$M$2:$M$1048576</definedName>
-    <definedName name="FC_Barcelona" localSheetId="5">BD!$C$2:$C$24</definedName>
+    <definedName name="FC_Barcelona" localSheetId="6">BD!$C$2:$C$24</definedName>
     <definedName name="FC_Barcelona">Lista!$C$2:$C$1048576</definedName>
     <definedName name="FcBarcelona">Lista!$C$2:$C$1048576</definedName>
-    <definedName name="Galatasaray" localSheetId="5">BD!$H$2:$H$24</definedName>
+    <definedName name="Galatasaray" localSheetId="6">BD!$H$2:$H$24</definedName>
     <definedName name="GALATASARAY">Lista!$I$2:$I$1048576</definedName>
-    <definedName name="Hellas_Verona" localSheetId="5">BD!$M$2:$M$24</definedName>
+    <definedName name="Hellas_Verona" localSheetId="6">BD!$M$2:$M$24</definedName>
     <definedName name="Hellas_Verona">Lista!$N$2:$N$1048576</definedName>
-    <definedName name="Inter_de_Milan" localSheetId="5">BD!$A$2:$A$24</definedName>
+    <definedName name="Inter_de_Milan" localSheetId="6">BD!$A$2:$A$24</definedName>
     <definedName name="Inter_de_Milan">Lista!$A$2:$A$1048576</definedName>
     <definedName name="InterMilan">Lista!$A$2:$A$1048576</definedName>
     <definedName name="Leverkusen">Lista!$F$2:$F$1048576</definedName>
-    <definedName name="Manchester_United" localSheetId="5">BD!$O$2:$O$24</definedName>
+    <definedName name="Manchester_United" localSheetId="6">BD!$O$2:$O$24</definedName>
     <definedName name="Manchester_United">Lista!$P$2:$P$1048576</definedName>
-    <definedName name="Melbourne_City" localSheetId="5">BD!#REF!</definedName>
+    <definedName name="Melbourne_City" localSheetId="6">BD!#REF!</definedName>
     <definedName name="Melbourne_City">Lista!$Q$2:$Q$1048576</definedName>
     <definedName name="PARIS_SAINT___GERMAIN">Lista!$J$2:$J$1048576</definedName>
-    <definedName name="PSG" localSheetId="5">BD!$I$2:$I$23</definedName>
+    <definedName name="PSG" localSheetId="6">BD!$I$2:$I$23</definedName>
     <definedName name="PSG">Lista!$K$2:$K$1048576</definedName>
-    <definedName name="RB_Leipzig" localSheetId="5">BD!$F$2:$F$24</definedName>
+    <definedName name="RB_Leipzig" localSheetId="6">BD!$F$2:$F$24</definedName>
     <definedName name="RB_LEIPZIG">Lista!$G$2:$G$1048576</definedName>
     <definedName name="RBLeipzig">Lista!$G$2:$G$1048576</definedName>
-    <definedName name="Real_Madrid" localSheetId="5">BD!$B$2:$B$24</definedName>
+    <definedName name="Real_Madrid" localSheetId="6">BD!$B$2:$B$24</definedName>
     <definedName name="Real_Madrid">Lista!$B$2:$B$1048576</definedName>
     <definedName name="RealMadrid">Lista!$B$2:$B$1048576</definedName>
     <definedName name="Sparta">Lista!$P$2:$P$1048576</definedName>
-    <definedName name="Terengganu_FC" localSheetId="5">BD!#REF!</definedName>
+    <definedName name="Terengganu_FC" localSheetId="6">BD!#REF!</definedName>
     <definedName name="Terengganu_FC">Lista!$D$2:$D$1048576</definedName>
     <definedName name="Terrengganu">Lista!$D$2:$D$1048576</definedName>
     <definedName name="Tottenham">Lista!$O$2:$O$1048576</definedName>
-    <definedName name="Tottenham_Hotspur" localSheetId="5">BD!$L$2:$L$24</definedName>
+    <definedName name="Tottenham_Hotspur" localSheetId="6">BD!$L$2:$L$24</definedName>
     <definedName name="Tottenham_Hotspur">Lista!$M$2:$M$1048576</definedName>
     <definedName name="United">Lista!$N$2:$N$1048576</definedName>
-    <definedName name="Wrexham" localSheetId="5">BD!$P$2:$P$24</definedName>
+    <definedName name="Wrexham" localSheetId="6">BD!$P$2:$P$24</definedName>
     <definedName name="WREXHAM">Lista!$R$2:$R$1048576</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -100,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2475" uniqueCount="1080">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2555" uniqueCount="1084">
   <si>
     <t>Equipo</t>
   </si>
@@ -3340,6 +3341,18 @@
   </si>
   <si>
     <t>Eder Militao</t>
+  </si>
+  <si>
+    <t>Valor</t>
+  </si>
+  <si>
+    <t>Epico</t>
+  </si>
+  <si>
+    <t>Big Time</t>
+  </si>
+  <si>
+    <t>CT Fabio Cannavaro</t>
   </si>
 </sst>
 </file>
@@ -3416,7 +3429,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3445,6 +3458,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -7122,6 +7138,314 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.77734375" customWidth="1"/>
+    <col min="8" max="10" width="8.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>997</v>
+      </c>
+      <c r="C1" t="s">
+        <v>998</v>
+      </c>
+      <c r="D1" t="s">
+        <v>999</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1001</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D3" t="s">
+        <v>229</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C4" t="s">
+        <v>234</v>
+      </c>
+      <c r="D4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" t="s">
+        <v>234</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C6" t="s">
+        <v>501</v>
+      </c>
+      <c r="D6" t="s">
+        <v>234</v>
+      </c>
+      <c r="E6">
+        <v>40</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>267</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C7" t="s">
+        <v>501</v>
+      </c>
+      <c r="D7" t="s">
+        <v>234</v>
+      </c>
+      <c r="E7">
+        <v>15</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C8" t="s">
+        <v>234</v>
+      </c>
+      <c r="D8" t="s">
+        <v>497</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C9" t="s">
+        <v>229</v>
+      </c>
+      <c r="D9" t="s">
+        <v>233</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C10" t="s">
+        <v>233</v>
+      </c>
+      <c r="D10" t="s">
+        <v>229</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>157</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D11" t="s">
+        <v>234</v>
+      </c>
+      <c r="E11">
+        <v>50</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C12" t="s">
+        <v>229</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>184</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D13" t="s">
+        <v>229</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G51" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7285,7 +7609,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:R24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8660,6 +8984,349 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86FCEC72-F57A-476F-86FC-E29836F3A0C3}">
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22.21875" customWidth="1"/>
+    <col min="3" max="3" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>997</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>1080</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>997</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>1080</v>
+      </c>
+      <c r="K1" s="5"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>596</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E2" s="3">
+        <v>103</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>690</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>1081</v>
+      </c>
+      <c r="I2" s="6">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>997</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1080</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>997</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>616</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E5" s="6">
+        <v>107</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>611</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>1081</v>
+      </c>
+      <c r="I5" s="6">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>997</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1080</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>997</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>915</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E8" s="6">
+        <v>102</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>698</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>1082</v>
+      </c>
+      <c r="I8" s="6">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>1081</v>
+      </c>
+      <c r="I9" s="6">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>997</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1080</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>1082</v>
+      </c>
+      <c r="I10" s="6">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>619</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E11" s="6">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>997</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>997</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1080</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>909</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>1081</v>
+      </c>
+      <c r="I13" s="6">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E14" s="6">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>571</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>1082</v>
+      </c>
+      <c r="E15" s="6">
+        <v>105</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>997</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>1083</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>1081</v>
+      </c>
+      <c r="I16" s="6">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>997</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C18" s="8" t="s">
+        <v>584</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E18" s="6">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C19" s="8" t="s">
+        <v>836</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>1082</v>
+      </c>
+      <c r="E19" s="6">
+        <v>105</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8833,7 +9500,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -9007,7 +9674,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D249"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -11360,7 +12027,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D250"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -13431,7 +14098,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:R24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -14805,7 +15472,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:AN24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -16179,7 +16846,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -16692,312 +17359,4 @@
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.77734375" customWidth="1"/>
-    <col min="8" max="10" width="8.77734375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" t="s">
-        <v>997</v>
-      </c>
-      <c r="C1" t="s">
-        <v>998</v>
-      </c>
-      <c r="D1" t="s">
-        <v>999</v>
-      </c>
-      <c r="E1" t="s">
-        <v>1000</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1001</v>
-      </c>
-      <c r="G1" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>464</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1003</v>
-      </c>
-      <c r="C2" t="s">
-        <v>229</v>
-      </c>
-      <c r="D2" t="s">
-        <v>1004</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>1006</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1003</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1004</v>
-      </c>
-      <c r="D3" t="s">
-        <v>229</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1003</v>
-      </c>
-      <c r="C4" t="s">
-        <v>234</v>
-      </c>
-      <c r="D4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B5" t="s">
-        <v>1003</v>
-      </c>
-      <c r="C5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D5" t="s">
-        <v>234</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>1007</v>
-      </c>
-      <c r="B6" t="s">
-        <v>1003</v>
-      </c>
-      <c r="C6" t="s">
-        <v>501</v>
-      </c>
-      <c r="D6" t="s">
-        <v>234</v>
-      </c>
-      <c r="E6">
-        <v>40</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="G6" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>267</v>
-      </c>
-      <c r="B7" t="s">
-        <v>1003</v>
-      </c>
-      <c r="C7" t="s">
-        <v>501</v>
-      </c>
-      <c r="D7" t="s">
-        <v>234</v>
-      </c>
-      <c r="E7">
-        <v>15</v>
-      </c>
-      <c r="F7">
-        <v>2</v>
-      </c>
-      <c r="G7" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>1008</v>
-      </c>
-      <c r="B8" t="s">
-        <v>1003</v>
-      </c>
-      <c r="C8" t="s">
-        <v>234</v>
-      </c>
-      <c r="D8" t="s">
-        <v>497</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>2</v>
-      </c>
-      <c r="G8" t="s">
-        <v>1009</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>1010</v>
-      </c>
-      <c r="B9" t="s">
-        <v>1003</v>
-      </c>
-      <c r="C9" t="s">
-        <v>229</v>
-      </c>
-      <c r="D9" t="s">
-        <v>233</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>2</v>
-      </c>
-      <c r="G9" t="s">
-        <v>1009</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>1011</v>
-      </c>
-      <c r="B10" t="s">
-        <v>1003</v>
-      </c>
-      <c r="C10" t="s">
-        <v>233</v>
-      </c>
-      <c r="D10" t="s">
-        <v>229</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>2</v>
-      </c>
-      <c r="G10" t="s">
-        <v>1009</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>157</v>
-      </c>
-      <c r="B11" t="s">
-        <v>1003</v>
-      </c>
-      <c r="C11" t="s">
-        <v>1004</v>
-      </c>
-      <c r="D11" t="s">
-        <v>234</v>
-      </c>
-      <c r="E11">
-        <v>50</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11" t="s">
-        <v>1009</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>1012</v>
-      </c>
-      <c r="B12" t="s">
-        <v>1003</v>
-      </c>
-      <c r="C12" t="s">
-        <v>229</v>
-      </c>
-      <c r="D12" t="s">
-        <v>1004</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12" t="s">
-        <v>1009</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>184</v>
-      </c>
-      <c r="B13" t="s">
-        <v>1003</v>
-      </c>
-      <c r="C13" t="s">
-        <v>1004</v>
-      </c>
-      <c r="D13" t="s">
-        <v>229</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="G13" t="s">
-        <v>1009</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:G51" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/LMI Base.xlsx
+++ b/LMI Base.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D61601FE-001E-4874-AA52-8337C6468984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32ACBB55-DAF9-4EF0-9387-56A43F50118F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro Liga" sheetId="1" r:id="rId1"/>
@@ -3429,7 +3429,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3458,9 +3458,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -9176,7 +9173,7 @@
       <c r="G10" s="3" t="s">
         <v>590</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="H10" s="3" t="s">
         <v>1082</v>
       </c>
       <c r="I10" s="6">
@@ -9227,7 +9224,7 @@
       <c r="G13" s="8" t="s">
         <v>909</v>
       </c>
-      <c r="H13" s="12" t="s">
+      <c r="H13" s="3" t="s">
         <v>1081</v>
       </c>
       <c r="I13" s="6">
@@ -9278,7 +9275,7 @@
       <c r="G16" s="6" t="s">
         <v>1083</v>
       </c>
-      <c r="H16" s="12" t="s">
+      <c r="H16" s="3" t="s">
         <v>1081</v>
       </c>
       <c r="I16" s="6">
@@ -16955,7 +16952,7 @@
         <v>100000000</v>
       </c>
       <c r="F4" s="7">
-        <v>8100000000</v>
+        <v>810000000</v>
       </c>
       <c r="G4" t="s">
         <v>937</v>

--- a/LMI Base.xlsx
+++ b/LMI Base.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32ACBB55-DAF9-4EF0-9387-56A43F50118F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEC00D50-E9E0-49E6-BDBA-40F1A959C766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro Liga" sheetId="1" r:id="rId1"/>
@@ -101,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2555" uniqueCount="1084">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2555" uniqueCount="1087">
   <si>
     <t>Equipo</t>
   </si>
@@ -1711,9 +1711,6 @@
     <t>LI Nuno Mendes</t>
   </si>
   <si>
-    <t>CT Antonio Rüdiger</t>
-  </si>
-  <si>
     <t>CT Emmanuel Agbadou</t>
   </si>
   <si>
@@ -2089,9 +2086,6 @@
     <t>ED Lionel Messi (P)</t>
   </si>
   <si>
-    <t>ED Lionel Messi</t>
-  </si>
-  <si>
     <t>ED Lamine Yamal</t>
   </si>
   <si>
@@ -2413,9 +2407,6 @@
     <t>MC Warren Zaïre-Emery</t>
   </si>
   <si>
-    <t>MCD Elliot Anderson</t>
-  </si>
-  <si>
     <t>LD Dodô</t>
   </si>
   <si>
@@ -2683,9 +2674,6 @@
     <t>EI Jérémy Doku</t>
   </si>
   <si>
-    <t>ID Phil Foden</t>
-  </si>
-  <si>
     <t>ID Ritsu Dōan</t>
   </si>
   <si>
@@ -3353,6 +3341,27 @@
   </si>
   <si>
     <t>CT Fabio Cannavaro</t>
+  </si>
+  <si>
+    <t>Amad Diallo</t>
+  </si>
+  <si>
+    <t>Phil Foden (P)</t>
+  </si>
+  <si>
+    <t>Brahim Díaz (P)</t>
+  </si>
+  <si>
+    <t>ID Denzel Dumfries</t>
+  </si>
+  <si>
+    <t>ID Brahim Díaz</t>
+  </si>
+  <si>
+    <t>MP Amad Diallo</t>
+  </si>
+  <si>
+    <t>ID Phil Foden (P)</t>
   </si>
 </sst>
 </file>
@@ -7154,22 +7163,22 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
+        <v>993</v>
+      </c>
+      <c r="C1" t="s">
+        <v>994</v>
+      </c>
+      <c r="D1" t="s">
+        <v>995</v>
+      </c>
+      <c r="E1" t="s">
+        <v>996</v>
+      </c>
+      <c r="F1" t="s">
         <v>997</v>
       </c>
-      <c r="C1" t="s">
+      <c r="G1" t="s">
         <v>998</v>
-      </c>
-      <c r="D1" t="s">
-        <v>999</v>
-      </c>
-      <c r="E1" t="s">
-        <v>1000</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1001</v>
-      </c>
-      <c r="G1" t="s">
-        <v>1002</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -7177,30 +7186,30 @@
         <v>464</v>
       </c>
       <c r="B2" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="C2" t="s">
         <v>229</v>
       </c>
       <c r="D2" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="B3" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="C3" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
       <c r="D3" t="s">
         <v>229</v>
@@ -7209,7 +7218,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -7217,7 +7226,7 @@
         <v>57</v>
       </c>
       <c r="B4" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="C4" t="s">
         <v>234</v>
@@ -7229,7 +7238,7 @@
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -7237,7 +7246,7 @@
         <v>66</v>
       </c>
       <c r="B5" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="C5" t="s">
         <v>55</v>
@@ -7249,15 +7258,15 @@
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="B6" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="C6" t="s">
         <v>501</v>
@@ -7272,7 +7281,7 @@
         <v>2</v>
       </c>
       <c r="G6" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -7280,7 +7289,7 @@
         <v>267</v>
       </c>
       <c r="B7" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="C7" t="s">
         <v>501</v>
@@ -7295,15 +7304,15 @@
         <v>2</v>
       </c>
       <c r="G7" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
       <c r="B8" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="C8" t="s">
         <v>234</v>
@@ -7318,15 +7327,15 @@
         <v>2</v>
       </c>
       <c r="G8" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>1010</v>
+        <v>1006</v>
       </c>
       <c r="B9" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="C9" t="s">
         <v>229</v>
@@ -7341,15 +7350,15 @@
         <v>2</v>
       </c>
       <c r="G9" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>1011</v>
+        <v>1007</v>
       </c>
       <c r="B10" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="C10" t="s">
         <v>233</v>
@@ -7364,7 +7373,7 @@
         <v>2</v>
       </c>
       <c r="G10" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -7372,10 +7381,10 @@
         <v>157</v>
       </c>
       <c r="B11" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="C11" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
       <c r="D11" t="s">
         <v>234</v>
@@ -7387,21 +7396,21 @@
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>1012</v>
+        <v>1008</v>
       </c>
       <c r="B12" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="C12" t="s">
         <v>229</v>
       </c>
       <c r="D12" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -7410,7 +7419,7 @@
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -7418,10 +7427,10 @@
         <v>184</v>
       </c>
       <c r="B13" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="C13" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
       <c r="D13" t="s">
         <v>229</v>
@@ -7433,7 +7442,7 @@
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
     </row>
   </sheetData>
@@ -7449,21 +7458,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>1013</v>
+        <v>1009</v>
       </c>
       <c r="B1" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="C1" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="B2" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -7471,10 +7480,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="B3" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -7482,10 +7491,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="B4" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -7493,10 +7502,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="B5" t="s">
-        <v>1019</v>
+        <v>1015</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -7504,10 +7513,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="B6" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -7515,10 +7524,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>1020</v>
+        <v>1016</v>
       </c>
       <c r="B7" t="s">
-        <v>1021</v>
+        <v>1017</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -7526,10 +7535,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>1020</v>
+        <v>1016</v>
       </c>
       <c r="B8" t="s">
-        <v>1022</v>
+        <v>1018</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -7537,10 +7546,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>1020</v>
+        <v>1016</v>
       </c>
       <c r="B9" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -7548,10 +7557,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>1020</v>
+        <v>1016</v>
       </c>
       <c r="B10" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -7559,10 +7568,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>1020</v>
+        <v>1016</v>
       </c>
       <c r="B11" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -7570,10 +7579,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>1023</v>
+        <v>1019</v>
       </c>
       <c r="B12" t="s">
-        <v>1019</v>
+        <v>1015</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -7581,10 +7590,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>1023</v>
+        <v>1019</v>
       </c>
       <c r="B13" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -7592,10 +7601,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>1023</v>
+        <v>1019</v>
       </c>
       <c r="B14" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -7707,7 +7716,7 @@
         <v>265</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>1024</v>
+        <v>1020</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>267</v>
@@ -7728,7 +7737,7 @@
         <v>272</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>274</v>
@@ -7748,10 +7757,10 @@
         <v>277</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>279</v>
@@ -7804,13 +7813,13 @@
         <v>289</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>1028</v>
+        <v>1024</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>1029</v>
+        <v>1025</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>292</v>
@@ -7819,7 +7828,7 @@
         <v>293</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>1031</v>
+        <v>1027</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>294</v>
@@ -7872,7 +7881,7 @@
         <v>306</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>1032</v>
+        <v>1028</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>326</v>
@@ -7896,7 +7905,7 @@
         <v>313</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>1033</v>
+        <v>1029</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>176</v>
@@ -7916,10 +7925,10 @@
         <v>316</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>1034</v>
+        <v>1030</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>317</v>
@@ -7955,7 +7964,7 @@
         <v>129</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="P6" s="3" t="s">
         <v>118</v>
@@ -8008,7 +8017,7 @@
         <v>330</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>1037</v>
+        <v>1033</v>
       </c>
       <c r="O7" s="3" t="s">
         <v>167</v>
@@ -8031,7 +8040,7 @@
         <v>249</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>1038</v>
+        <v>1034</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>191</v>
@@ -8058,7 +8067,7 @@
         <v>169</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>1039</v>
+        <v>1035</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>131</v>
@@ -8137,13 +8146,13 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>1040</v>
+        <v>1036</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>1041</v>
+        <v>1037</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>140</v>
@@ -8179,7 +8188,7 @@
         <v>57</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>1042</v>
+        <v>1038</v>
       </c>
       <c r="P10" s="3" t="s">
         <v>155</v>
@@ -8252,7 +8261,7 @@
         <v>54</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>1043</v>
+        <v>1039</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>192</v>
@@ -8264,10 +8273,10 @@
         <v>53</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>1044</v>
+        <v>1040</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>1045</v>
+        <v>1041</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>82</v>
@@ -8305,7 +8314,7 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>440</v>
@@ -8323,7 +8332,7 @@
         <v>84</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>370</v>
@@ -8338,7 +8347,7 @@
         <v>372</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>1048</v>
+        <v>1044</v>
       </c>
       <c r="M13" s="3" t="s">
         <v>374</v>
@@ -8350,7 +8359,7 @@
         <v>376</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="Q13" s="3" t="s">
         <v>377</v>
@@ -8361,13 +8370,13 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>211</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>380</v>
@@ -8376,10 +8385,10 @@
         <v>381</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>382</v>
@@ -8400,10 +8409,10 @@
         <v>387</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>390</v>
@@ -8417,13 +8426,13 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>1056</v>
+        <v>1052</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>1057</v>
+        <v>1053</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>369</v>
@@ -8479,7 +8488,7 @@
         <v>189</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>1058</v>
+        <v>1054</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>106</v>
@@ -8491,7 +8500,7 @@
         <v>114</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>1059</v>
+        <v>1055</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>410</v>
@@ -8506,7 +8515,7 @@
         <v>412</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>157</v>
@@ -8518,7 +8527,7 @@
         <v>404</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
       <c r="Q16" s="3" t="s">
         <v>257</v>
@@ -8544,7 +8553,7 @@
         <v>420</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>205</v>
@@ -8562,7 +8571,7 @@
         <v>424</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>1063</v>
+        <v>1059</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>425</v>
@@ -8588,7 +8597,7 @@
         <v>431</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>1064</v>
+        <v>1060</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>246</v>
@@ -8603,7 +8612,7 @@
         <v>175</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>1065</v>
+        <v>1061</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>435</v>
@@ -8644,7 +8653,7 @@
         <v>470</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>1066</v>
+        <v>1062</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>117</v>
@@ -8659,7 +8668,7 @@
         <v>170</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>444</v>
@@ -8686,7 +8695,7 @@
         <v>73</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
       <c r="Q19" s="3" t="s">
         <v>450</v>
@@ -8700,7 +8709,7 @@
         <v>135</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>1069</v>
+        <v>1065</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>202</v>
@@ -8756,7 +8765,7 @@
         <v>22</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>1070</v>
+        <v>1066</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>178</v>
@@ -8771,7 +8780,7 @@
         <v>460</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>1071</v>
+        <v>1067</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>461</v>
@@ -8798,7 +8807,7 @@
         <v>187</v>
       </c>
       <c r="P21" s="3" t="s">
-        <v>1072</v>
+        <v>1068</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>196</v>
@@ -8815,16 +8824,16 @@
         <v>477</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>1074</v>
+        <v>1070</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>152</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>1075</v>
+        <v>1071</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>204</v>
@@ -8865,7 +8874,7 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>141</v>
@@ -8892,7 +8901,7 @@
         <v>64</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>1077</v>
+        <v>1073</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>39</v>
@@ -8924,10 +8933,10 @@
         <v>486</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>1079</v>
+        <v>1075</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>46</v>
@@ -9002,19 +9011,19 @@
         <v>20</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>51</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
       <c r="K1" s="5"/>
     </row>
@@ -9023,19 +9032,19 @@
         <v>4</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="E2" s="3">
         <v>103</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="I2" s="6">
         <v>101</v>
@@ -9054,19 +9063,19 @@
         <v>32</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>44</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -9074,19 +9083,19 @@
         <v>51</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="E5" s="6">
         <v>107</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="I5" s="6">
         <v>101</v>
@@ -9105,19 +9114,19 @@
         <v>55</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>119</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
@@ -9125,19 +9134,19 @@
         <v>36</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="E8" s="6">
         <v>102</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
       <c r="I8" s="6">
         <v>106</v>
@@ -9148,10 +9157,10 @@
         <v>7</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="I9" s="6">
         <v>103</v>
@@ -9165,16 +9174,16 @@
         <v>49</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
       <c r="I10" s="6">
         <v>102</v>
@@ -9185,10 +9194,10 @@
         <v>26</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="E11" s="6">
         <v>104</v>
@@ -9202,10 +9211,10 @@
         <v>36</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -9216,16 +9225,16 @@
         <v>26</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="I13" s="6">
         <v>107</v>
@@ -9236,10 +9245,10 @@
         <v>40</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="E14" s="6">
         <v>106</v>
@@ -9250,10 +9259,10 @@
         <v>44</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
       <c r="E15" s="6">
         <v>105</v>
@@ -9262,10 +9271,10 @@
         <v>193</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
@@ -9273,10 +9282,10 @@
         <v>193</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="I16" s="6">
         <v>105</v>
@@ -9290,18 +9299,18 @@
         <v>69</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C18" s="8" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="E18" s="6">
         <v>103</v>
@@ -9309,10 +9318,10 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C19" s="8" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
       <c r="E19" s="6">
         <v>105</v>
@@ -14270,7 +14279,7 @@
         <v>30</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>287</v>
+        <v>186</v>
       </c>
       <c r="N3" s="3" t="s">
         <v>99</v>
@@ -14662,7 +14671,7 @@
         <v>355</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>184</v>
+        <v>1082</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>57</v>
@@ -14998,7 +15007,7 @@
         <v>413</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>157</v>
+        <v>425</v>
       </c>
       <c r="N16" s="3" t="s">
         <v>414</v>
@@ -15054,7 +15063,7 @@
         <v>201</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>425</v>
+        <v>212</v>
       </c>
       <c r="N17" s="3" t="s">
         <v>426</v>
@@ -15110,7 +15119,7 @@
         <v>436</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>212</v>
+        <v>1080</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>105</v>
@@ -15278,7 +15287,7 @@
         <v>162</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>464</v>
+        <v>1081</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>465</v>
@@ -15531,7 +15540,7 @@
       <c r="L1" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="8" t="s">
         <v>503</v>
       </c>
       <c r="N1" s="8" t="s">
@@ -15587,7 +15596,7 @@
       <c r="L2" s="8" t="s">
         <v>517</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M2" s="8" t="s">
         <v>518</v>
       </c>
       <c r="N2" s="8" t="s">
@@ -15643,1199 +15652,1199 @@
       <c r="L3" s="8" t="s">
         <v>535</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="8" t="s">
+        <v>1083</v>
+      </c>
+      <c r="N3" s="8" t="s">
         <v>536</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="O3" s="8" t="s">
         <v>537</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="P3" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="P3" s="8" t="s">
+      <c r="Q3" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="R3" s="8" t="s">
         <v>540</v>
-      </c>
-      <c r="R3" s="8" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
+        <v>541</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>542</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="C4" s="8" t="s">
         <v>543</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="D4" s="8" t="s">
         <v>544</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="E4" s="8" t="s">
         <v>545</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="F4" s="8" t="s">
         <v>546</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="G4" s="8" t="s">
         <v>547</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="H4" s="8" t="s">
         <v>548</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="I4" s="8" t="s">
         <v>549</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="J4" s="8" t="s">
         <v>550</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="K4" s="8" t="s">
         <v>551</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="L4" s="8" t="s">
         <v>552</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="M4" s="8" t="s">
         <v>553</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="N4" s="8" t="s">
         <v>554</v>
       </c>
-      <c r="N4" s="8" t="s">
+      <c r="O4" s="8" t="s">
         <v>555</v>
       </c>
-      <c r="O4" s="8" t="s">
+      <c r="P4" s="8" t="s">
         <v>556</v>
       </c>
-      <c r="P4" s="8" t="s">
+      <c r="Q4" s="3" t="s">
         <v>557</v>
       </c>
-      <c r="Q4" s="3" t="s">
+      <c r="R4" s="8" t="s">
         <v>558</v>
-      </c>
-      <c r="R4" s="8" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
+        <v>559</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>560</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="C5" s="8" t="s">
         <v>561</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="D5" s="8" t="s">
         <v>562</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="E5" s="8" t="s">
         <v>563</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="F5" s="8" t="s">
         <v>564</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="G5" s="8" t="s">
         <v>565</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="H5" s="8" t="s">
         <v>566</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="I5" s="8" t="s">
         <v>567</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="J5" s="8" t="s">
         <v>568</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="K5" s="8" t="s">
         <v>569</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="L5" s="8" t="s">
         <v>570</v>
       </c>
-      <c r="L5" s="8" t="s">
+      <c r="M5" s="8" t="s">
         <v>571</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="N5" s="8" t="s">
         <v>572</v>
       </c>
-      <c r="N5" s="8" t="s">
+      <c r="O5" s="8" t="s">
         <v>573</v>
       </c>
-      <c r="O5" s="8" t="s">
+      <c r="P5" s="8" t="s">
         <v>574</v>
       </c>
-      <c r="P5" s="8" t="s">
+      <c r="Q5" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="Q5" s="3" t="s">
+      <c r="R5" s="8" t="s">
         <v>576</v>
-      </c>
-      <c r="R5" s="8" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
+        <v>577</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>578</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="C6" s="8" t="s">
         <v>579</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="D6" s="8" t="s">
         <v>580</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="E6" s="8" t="s">
         <v>581</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="F6" s="8" t="s">
         <v>582</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="G6" s="8" t="s">
         <v>583</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="H6" s="8" t="s">
         <v>584</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="I6" s="8" t="s">
         <v>585</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="J6" s="8" t="s">
         <v>586</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="K6" s="8" t="s">
         <v>587</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="L6" s="8" t="s">
         <v>588</v>
       </c>
-      <c r="L6" s="8" t="s">
+      <c r="M6" s="8" t="s">
         <v>589</v>
       </c>
-      <c r="M6" s="3" t="s">
+      <c r="N6" s="8" t="s">
         <v>590</v>
       </c>
-      <c r="N6" s="8" t="s">
+      <c r="O6" s="8" t="s">
         <v>591</v>
       </c>
-      <c r="O6" s="8" t="s">
+      <c r="P6" s="8" t="s">
         <v>592</v>
       </c>
-      <c r="P6" s="8" t="s">
+      <c r="Q6" s="3" t="s">
         <v>593</v>
       </c>
-      <c r="Q6" s="3" t="s">
+      <c r="R6" s="8" t="s">
         <v>594</v>
-      </c>
-      <c r="R6" s="8" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
+        <v>595</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>596</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="C7" s="8" t="s">
         <v>597</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="D7" s="8" t="s">
         <v>598</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="E7" s="8" t="s">
         <v>599</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="F7" s="8" t="s">
         <v>600</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="G7" s="8" t="s">
         <v>601</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="H7" s="8" t="s">
         <v>602</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="I7" s="8" t="s">
         <v>603</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="J7" s="8" t="s">
         <v>604</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="K7" s="8" t="s">
         <v>605</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="L7" s="8" t="s">
         <v>606</v>
       </c>
-      <c r="L7" s="8" t="s">
+      <c r="M7" s="8" t="s">
         <v>607</v>
       </c>
-      <c r="M7" s="3" t="s">
+      <c r="N7" s="8" t="s">
         <v>608</v>
       </c>
-      <c r="N7" s="8" t="s">
+      <c r="O7" s="8" t="s">
         <v>609</v>
       </c>
-      <c r="O7" s="8" t="s">
+      <c r="P7" s="8" t="s">
         <v>610</v>
       </c>
-      <c r="P7" s="8" t="s">
+      <c r="Q7" s="3" t="s">
         <v>611</v>
       </c>
-      <c r="Q7" s="3" t="s">
+      <c r="R7" s="8" t="s">
         <v>612</v>
-      </c>
-      <c r="R7" s="8" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
+        <v>613</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>614</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="C8" s="8" t="s">
         <v>615</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="D8" s="8" t="s">
         <v>616</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="E8" s="8" t="s">
         <v>617</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="F8" s="8" t="s">
         <v>618</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="G8" s="8" t="s">
         <v>619</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="H8" s="8" t="s">
         <v>620</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="I8" s="8" t="s">
         <v>621</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="J8" s="8" t="s">
         <v>622</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="K8" s="8" t="s">
         <v>623</v>
       </c>
-      <c r="K8" s="8" t="s">
+      <c r="L8" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="L8" s="8" t="s">
+      <c r="M8" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="M8" s="3" t="s">
+      <c r="N8" s="8" t="s">
         <v>626</v>
       </c>
-      <c r="N8" s="8" t="s">
+      <c r="O8" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="O8" s="8" t="s">
+      <c r="P8" s="8" t="s">
         <v>628</v>
       </c>
-      <c r="P8" s="8" t="s">
+      <c r="Q8" s="3" t="s">
         <v>629</v>
       </c>
-      <c r="Q8" s="3" t="s">
+      <c r="R8" s="8" t="s">
         <v>630</v>
-      </c>
-      <c r="R8" s="8" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
+        <v>631</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>632</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="C9" s="8" t="s">
         <v>633</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="D9" s="8" t="s">
         <v>634</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="E9" s="8" t="s">
         <v>635</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="F9" s="8" t="s">
         <v>636</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="G9" s="8" t="s">
         <v>637</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="H9" s="8" t="s">
         <v>638</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="I9" s="8" t="s">
         <v>639</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="J9" s="8" t="s">
         <v>640</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="K9" s="8" t="s">
         <v>641</v>
       </c>
-      <c r="K9" s="8" t="s">
+      <c r="L9" s="8" t="s">
         <v>642</v>
       </c>
-      <c r="L9" s="8" t="s">
+      <c r="M9" s="8" t="s">
         <v>643</v>
       </c>
-      <c r="M9" s="3" t="s">
+      <c r="N9" s="8" t="s">
         <v>644</v>
       </c>
-      <c r="N9" s="8" t="s">
+      <c r="O9" s="8" t="s">
         <v>645</v>
       </c>
-      <c r="O9" s="8" t="s">
+      <c r="P9" s="8" t="s">
         <v>646</v>
       </c>
-      <c r="P9" s="8" t="s">
+      <c r="Q9" s="3" t="s">
         <v>647</v>
       </c>
-      <c r="Q9" s="3" t="s">
+      <c r="R9" s="8" t="s">
         <v>648</v>
-      </c>
-      <c r="R9" s="8" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
+        <v>649</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>650</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="C10" s="8" t="s">
         <v>651</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="D10" s="8" t="s">
         <v>652</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="E10" s="8" t="s">
         <v>653</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="F10" s="8" t="s">
         <v>654</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="G10" s="8" t="s">
         <v>655</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="H10" s="8" t="s">
         <v>656</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="I10" s="8" t="s">
         <v>657</v>
       </c>
-      <c r="I10" s="8" t="s">
+      <c r="J10" s="8" t="s">
         <v>658</v>
       </c>
-      <c r="J10" s="8" t="s">
+      <c r="K10" s="8" t="s">
         <v>659</v>
       </c>
-      <c r="K10" s="8" t="s">
+      <c r="L10" s="8" t="s">
         <v>660</v>
       </c>
-      <c r="L10" s="8" t="s">
+      <c r="M10" s="8" t="s">
+        <v>1084</v>
+      </c>
+      <c r="N10" s="8" t="s">
         <v>661</v>
       </c>
-      <c r="M10" s="3" t="s">
+      <c r="O10" s="8" t="s">
         <v>662</v>
       </c>
-      <c r="N10" s="8" t="s">
+      <c r="P10" s="8" t="s">
         <v>663</v>
       </c>
-      <c r="O10" s="8" t="s">
+      <c r="Q10" s="3" t="s">
         <v>664</v>
       </c>
-      <c r="P10" s="8" t="s">
+      <c r="R10" s="8" t="s">
         <v>665</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>666</v>
-      </c>
-      <c r="R10" s="8" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
+        <v>666</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>667</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>668</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="D11" s="8" t="s">
         <v>669</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="E11" s="8" t="s">
         <v>670</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="F11" s="8" t="s">
         <v>671</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="G11" s="8" t="s">
         <v>672</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="H11" s="8" t="s">
         <v>673</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="I11" s="8" t="s">
         <v>674</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="J11" s="8" t="s">
         <v>675</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="K11" s="8" t="s">
         <v>676</v>
       </c>
-      <c r="J11" s="8" t="s">
+      <c r="L11" s="8" t="s">
         <v>677</v>
       </c>
-      <c r="K11" s="8" t="s">
+      <c r="M11" s="8" t="s">
         <v>678</v>
       </c>
-      <c r="L11" s="8" t="s">
+      <c r="N11" s="8" t="s">
         <v>679</v>
       </c>
-      <c r="M11" s="3" t="s">
+      <c r="O11" s="8" t="s">
         <v>680</v>
       </c>
-      <c r="N11" s="8" t="s">
+      <c r="P11" s="8" t="s">
         <v>681</v>
       </c>
-      <c r="O11" s="8" t="s">
+      <c r="Q11" s="3" t="s">
         <v>682</v>
       </c>
-      <c r="P11" s="8" t="s">
+      <c r="R11" s="8" t="s">
         <v>683</v>
-      </c>
-      <c r="Q11" s="3" t="s">
-        <v>684</v>
-      </c>
-      <c r="R11" s="8" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
+        <v>684</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>685</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>686</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="D12" s="8" t="s">
         <v>687</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="E12" s="8" t="s">
         <v>688</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="F12" s="8" t="s">
         <v>689</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="G12" s="8" t="s">
         <v>690</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="H12" s="8" t="s">
         <v>691</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="I12" s="8" t="s">
         <v>692</v>
       </c>
-      <c r="H12" s="8" t="s">
+      <c r="J12" s="8" t="s">
         <v>693</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="K12" s="8" t="s">
         <v>694</v>
       </c>
-      <c r="J12" s="8" t="s">
+      <c r="L12" s="8" t="s">
         <v>695</v>
       </c>
-      <c r="K12" s="8" t="s">
+      <c r="M12" s="8" t="s">
         <v>696</v>
       </c>
-      <c r="L12" s="8" t="s">
+      <c r="N12" s="8" t="s">
         <v>697</v>
       </c>
-      <c r="M12" s="3" t="s">
+      <c r="O12" s="8" t="s">
         <v>698</v>
       </c>
-      <c r="N12" s="8" t="s">
+      <c r="P12" s="8" t="s">
         <v>699</v>
       </c>
-      <c r="O12" s="8" t="s">
+      <c r="Q12" s="3" t="s">
         <v>700</v>
       </c>
-      <c r="P12" s="8" t="s">
+      <c r="R12" s="8" t="s">
         <v>701</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>702</v>
-      </c>
-      <c r="R12" s="8" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
+        <v>702</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>703</v>
+      </c>
+      <c r="C13" s="8" t="s">
         <v>704</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="D13" s="8" t="s">
         <v>705</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="E13" s="8" t="s">
         <v>706</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="F13" s="8" t="s">
         <v>707</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="G13" s="8" t="s">
         <v>708</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="H13" s="8" t="s">
         <v>709</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="I13" s="8" t="s">
         <v>710</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="J13" s="8" t="s">
         <v>711</v>
       </c>
-      <c r="I13" s="8" t="s">
+      <c r="K13" s="8" t="s">
         <v>712</v>
       </c>
-      <c r="J13" s="8" t="s">
+      <c r="L13" s="8" t="s">
         <v>713</v>
       </c>
-      <c r="K13" s="8" t="s">
+      <c r="M13" s="8" t="s">
         <v>714</v>
       </c>
-      <c r="L13" s="8" t="s">
+      <c r="N13" s="8" t="s">
         <v>715</v>
       </c>
-      <c r="M13" s="3" t="s">
+      <c r="O13" s="8" t="s">
         <v>716</v>
       </c>
-      <c r="N13" s="8" t="s">
+      <c r="P13" s="8" t="s">
         <v>717</v>
       </c>
-      <c r="O13" s="8" t="s">
+      <c r="Q13" s="3" t="s">
         <v>718</v>
       </c>
-      <c r="P13" s="8" t="s">
+      <c r="R13" s="8" t="s">
         <v>719</v>
-      </c>
-      <c r="Q13" s="3" t="s">
-        <v>720</v>
-      </c>
-      <c r="R13" s="8" t="s">
-        <v>721</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
+        <v>720</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>722</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="D14" s="8" t="s">
         <v>723</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="E14" s="8" t="s">
         <v>724</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="F14" s="8" t="s">
         <v>725</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="G14" s="8" t="s">
         <v>726</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="H14" s="8" t="s">
         <v>727</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="I14" s="9" t="s">
         <v>728</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="J14" s="8" t="s">
         <v>729</v>
       </c>
-      <c r="I14" s="9" t="s">
+      <c r="K14" s="8" t="s">
         <v>730</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="L14" s="8" t="s">
         <v>731</v>
       </c>
-      <c r="K14" s="8" t="s">
+      <c r="M14" s="8" t="s">
         <v>732</v>
       </c>
-      <c r="L14" s="8" t="s">
+      <c r="N14" s="8" t="s">
         <v>733</v>
       </c>
-      <c r="M14" s="3" t="s">
+      <c r="O14" s="8" t="s">
         <v>734</v>
       </c>
-      <c r="N14" s="8" t="s">
+      <c r="P14" s="8" t="s">
         <v>735</v>
       </c>
-      <c r="O14" s="8" t="s">
+      <c r="Q14" s="3" t="s">
         <v>736</v>
       </c>
-      <c r="P14" s="8" t="s">
+      <c r="R14" s="8" t="s">
         <v>737</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>738</v>
-      </c>
-      <c r="R14" s="8" t="s">
-        <v>739</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
+        <v>738</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>739</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>740</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="D15" s="8" t="s">
         <v>741</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="E15" s="8" t="s">
         <v>742</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="F15" s="8" t="s">
         <v>743</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="G15" s="8" t="s">
         <v>744</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="H15" s="8" t="s">
         <v>745</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="I15" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="H15" s="8" t="s">
+      <c r="J15" s="8" t="s">
         <v>747</v>
       </c>
-      <c r="I15" s="8" t="s">
+      <c r="K15" s="8" t="s">
         <v>748</v>
       </c>
-      <c r="J15" s="8" t="s">
+      <c r="L15" s="8" t="s">
         <v>749</v>
       </c>
-      <c r="K15" s="8" t="s">
+      <c r="M15" s="8" t="s">
         <v>750</v>
       </c>
-      <c r="L15" s="8" t="s">
+      <c r="N15" s="8" t="s">
         <v>751</v>
       </c>
-      <c r="M15" s="3" t="s">
+      <c r="O15" s="8" t="s">
         <v>752</v>
       </c>
-      <c r="N15" s="8" t="s">
+      <c r="P15" s="8" t="s">
         <v>753</v>
       </c>
-      <c r="O15" s="8" t="s">
+      <c r="Q15" s="3" t="s">
         <v>754</v>
       </c>
-      <c r="P15" s="8" t="s">
+      <c r="R15" s="8" t="s">
         <v>755</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>756</v>
-      </c>
-      <c r="R15" s="8" t="s">
-        <v>757</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
+        <v>756</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>757</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="D16" s="8" t="s">
         <v>759</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="E16" s="8" t="s">
         <v>760</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="F16" s="8" t="s">
         <v>761</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="G16" s="8" t="s">
         <v>762</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="H16" s="8" t="s">
         <v>763</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="I16" s="8" t="s">
         <v>764</v>
       </c>
-      <c r="H16" s="8" t="s">
+      <c r="J16" s="8" t="s">
         <v>765</v>
       </c>
-      <c r="I16" s="8" t="s">
+      <c r="K16" s="8" t="s">
         <v>766</v>
       </c>
-      <c r="J16" s="8" t="s">
+      <c r="L16" s="8" t="s">
         <v>767</v>
       </c>
-      <c r="K16" s="8" t="s">
+      <c r="M16" s="8" t="s">
+        <v>785</v>
+      </c>
+      <c r="N16" s="8" t="s">
         <v>768</v>
       </c>
-      <c r="L16" s="8" t="s">
+      <c r="O16" s="8" t="s">
         <v>769</v>
       </c>
-      <c r="M16" s="3" t="s">
+      <c r="P16" s="8" t="s">
         <v>770</v>
       </c>
-      <c r="N16" s="8" t="s">
+      <c r="Q16" s="3" t="s">
         <v>771</v>
       </c>
-      <c r="O16" s="8" t="s">
+      <c r="R16" s="8" t="s">
         <v>772</v>
-      </c>
-      <c r="P16" s="8" t="s">
-        <v>773</v>
-      </c>
-      <c r="Q16" s="3" t="s">
-        <v>774</v>
-      </c>
-      <c r="R16" s="8" t="s">
-        <v>775</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
+        <v>773</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>774</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>775</v>
+      </c>
+      <c r="D17" s="8" t="s">
         <v>776</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="E17" s="8" t="s">
         <v>777</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="F17" s="8" t="s">
         <v>778</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="G17" s="8" t="s">
         <v>779</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="H17" s="8" t="s">
         <v>780</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="I17" s="8" t="s">
         <v>781</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="J17" s="8" t="s">
         <v>782</v>
       </c>
-      <c r="H17" s="8" t="s">
+      <c r="K17" s="8" t="s">
         <v>783</v>
       </c>
-      <c r="I17" s="8" t="s">
+      <c r="L17" s="8" t="s">
         <v>784</v>
       </c>
-      <c r="J17" s="8" t="s">
-        <v>785</v>
-      </c>
-      <c r="K17" s="8" t="s">
+      <c r="M17" s="8" t="s">
+        <v>803</v>
+      </c>
+      <c r="N17" s="8" t="s">
         <v>786</v>
       </c>
-      <c r="L17" s="8" t="s">
+      <c r="O17" s="8" t="s">
         <v>787</v>
       </c>
-      <c r="M17" s="3" t="s">
+      <c r="P17" s="8" t="s">
         <v>788</v>
       </c>
-      <c r="N17" s="8" t="s">
+      <c r="Q17" s="3" t="s">
         <v>789</v>
       </c>
-      <c r="O17" s="8" t="s">
+      <c r="R17" s="8" t="s">
         <v>790</v>
-      </c>
-      <c r="P17" s="8" t="s">
-        <v>791</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>792</v>
-      </c>
-      <c r="R17" s="8" t="s">
-        <v>793</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
+        <v>791</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>792</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>793</v>
+      </c>
+      <c r="D18" s="8" t="s">
         <v>794</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="E18" s="8" t="s">
         <v>795</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="F18" s="8" t="s">
         <v>796</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="G18" s="8" t="s">
         <v>797</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="H18" s="8" t="s">
         <v>798</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="I18" s="8" t="s">
         <v>799</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="J18" s="8" t="s">
         <v>800</v>
       </c>
-      <c r="H18" s="8" t="s">
+      <c r="K18" s="8" t="s">
         <v>801</v>
       </c>
-      <c r="I18" s="8" t="s">
+      <c r="L18" s="8" t="s">
         <v>802</v>
       </c>
-      <c r="J18" s="8" t="s">
-        <v>803</v>
-      </c>
-      <c r="K18" s="8" t="s">
+      <c r="M18" s="8" t="s">
+        <v>1085</v>
+      </c>
+      <c r="N18" s="8" t="s">
         <v>804</v>
       </c>
-      <c r="L18" s="8" t="s">
+      <c r="O18" s="8" t="s">
         <v>805</v>
       </c>
-      <c r="M18" s="3" t="s">
+      <c r="P18" s="8" t="s">
         <v>806</v>
       </c>
-      <c r="N18" s="8" t="s">
+      <c r="Q18" s="3" t="s">
         <v>807</v>
       </c>
-      <c r="O18" s="8" t="s">
+      <c r="R18" s="8" t="s">
         <v>808</v>
-      </c>
-      <c r="P18" s="8" t="s">
-        <v>809</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>810</v>
-      </c>
-      <c r="R18" s="8" t="s">
-        <v>811</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
+        <v>809</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>810</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>811</v>
+      </c>
+      <c r="D19" s="8" t="s">
         <v>812</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="E19" s="8" t="s">
         <v>813</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="F19" s="8" t="s">
         <v>814</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="G19" s="8" t="s">
         <v>815</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="H19" s="8" t="s">
         <v>816</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="I19" s="8" t="s">
         <v>817</v>
       </c>
-      <c r="G19" s="8" t="s">
+      <c r="J19" s="8" t="s">
         <v>818</v>
       </c>
-      <c r="H19" s="8" t="s">
+      <c r="K19" s="8" t="s">
         <v>819</v>
       </c>
-      <c r="I19" s="8" t="s">
+      <c r="L19" s="8" t="s">
         <v>820</v>
       </c>
-      <c r="J19" s="8" t="s">
+      <c r="M19" s="8" t="s">
         <v>821</v>
       </c>
-      <c r="K19" s="8" t="s">
+      <c r="N19" s="8" t="s">
         <v>822</v>
       </c>
-      <c r="L19" s="8" t="s">
+      <c r="O19" s="8" t="s">
         <v>823</v>
       </c>
-      <c r="M19" s="3" t="s">
+      <c r="P19" s="8" t="s">
         <v>824</v>
       </c>
-      <c r="N19" s="8" t="s">
+      <c r="Q19" s="3" t="s">
         <v>825</v>
       </c>
-      <c r="O19" s="8" t="s">
+      <c r="R19" s="8" t="s">
         <v>826</v>
-      </c>
-      <c r="P19" s="8" t="s">
-        <v>827</v>
-      </c>
-      <c r="Q19" s="3" t="s">
-        <v>828</v>
-      </c>
-      <c r="R19" s="8" t="s">
-        <v>829</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
+        <v>827</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>828</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>829</v>
+      </c>
+      <c r="D20" s="8" t="s">
         <v>830</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="E20" s="8" t="s">
         <v>831</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="F20" s="8" t="s">
         <v>832</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="G20" s="8" t="s">
         <v>833</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="H20" s="8" t="s">
         <v>834</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="I20" s="8" t="s">
         <v>835</v>
       </c>
-      <c r="G20" s="8" t="s">
+      <c r="J20" s="8" t="s">
         <v>836</v>
       </c>
-      <c r="H20" s="8" t="s">
+      <c r="K20" s="8" t="s">
         <v>837</v>
       </c>
-      <c r="I20" s="8" t="s">
+      <c r="L20" s="8" t="s">
         <v>838</v>
       </c>
-      <c r="J20" s="8" t="s">
+      <c r="M20" s="8" t="s">
         <v>839</v>
       </c>
-      <c r="K20" s="8" t="s">
+      <c r="N20" s="8" t="s">
         <v>840</v>
       </c>
-      <c r="L20" s="8" t="s">
+      <c r="O20" s="8" t="s">
         <v>841</v>
       </c>
-      <c r="M20" s="3" t="s">
+      <c r="P20" s="9" t="s">
         <v>842</v>
       </c>
-      <c r="N20" s="8" t="s">
+      <c r="Q20" s="3" t="s">
         <v>843</v>
       </c>
-      <c r="O20" s="8" t="s">
+      <c r="R20" s="8" t="s">
         <v>844</v>
-      </c>
-      <c r="P20" s="9" t="s">
-        <v>845</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>846</v>
-      </c>
-      <c r="R20" s="8" t="s">
-        <v>847</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
+        <v>845</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>846</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>847</v>
+      </c>
+      <c r="D21" s="8" t="s">
         <v>848</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="E21" s="8" t="s">
         <v>849</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="F21" s="8" t="s">
         <v>850</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="G21" s="8" t="s">
         <v>851</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="H21" s="8" t="s">
         <v>852</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="I21" s="8" t="s">
         <v>853</v>
       </c>
-      <c r="G21" s="8" t="s">
+      <c r="J21" s="8" t="s">
         <v>854</v>
       </c>
-      <c r="H21" s="8" t="s">
+      <c r="K21" s="8" t="s">
         <v>855</v>
       </c>
-      <c r="I21" s="8" t="s">
+      <c r="L21" s="8" t="s">
         <v>856</v>
       </c>
-      <c r="J21" s="8" t="s">
+      <c r="M21" s="8" t="s">
+        <v>1086</v>
+      </c>
+      <c r="N21" s="8" t="s">
         <v>857</v>
       </c>
-      <c r="K21" s="8" t="s">
+      <c r="O21" s="8" t="s">
         <v>858</v>
       </c>
-      <c r="L21" s="8" t="s">
+      <c r="P21" s="8" t="s">
         <v>859</v>
       </c>
-      <c r="M21" s="3" t="s">
+      <c r="Q21" s="3" t="s">
         <v>860</v>
       </c>
-      <c r="N21" s="8" t="s">
+      <c r="R21" s="8" t="s">
         <v>861</v>
-      </c>
-      <c r="O21" s="8" t="s">
-        <v>862</v>
-      </c>
-      <c r="P21" s="8" t="s">
-        <v>863</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>864</v>
-      </c>
-      <c r="R21" s="8" t="s">
-        <v>865</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
+        <v>862</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>863</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>864</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>865</v>
+      </c>
+      <c r="E22" s="8" t="s">
         <v>866</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="F22" s="8" t="s">
         <v>867</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="G22" s="8" t="s">
         <v>868</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="H22" s="8" t="s">
         <v>869</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="I22" s="8" t="s">
         <v>870</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="J22" s="8" t="s">
         <v>871</v>
       </c>
-      <c r="G22" s="8" t="s">
+      <c r="K22" s="8" t="s">
         <v>872</v>
       </c>
-      <c r="H22" s="8" t="s">
+      <c r="L22" s="8" t="s">
         <v>873</v>
       </c>
-      <c r="I22" s="8" t="s">
+      <c r="M22" s="8" t="s">
         <v>874</v>
       </c>
-      <c r="J22" s="8" t="s">
+      <c r="N22" s="8" t="s">
         <v>875</v>
       </c>
-      <c r="K22" s="8" t="s">
+      <c r="O22" s="8" t="s">
         <v>876</v>
       </c>
-      <c r="L22" s="8" t="s">
+      <c r="P22" s="8" t="s">
         <v>877</v>
       </c>
-      <c r="M22" s="3" t="s">
+      <c r="Q22" s="3" t="s">
         <v>878</v>
       </c>
-      <c r="N22" s="8" t="s">
+      <c r="R22" s="8" t="s">
         <v>879</v>
-      </c>
-      <c r="O22" s="8" t="s">
-        <v>880</v>
-      </c>
-      <c r="P22" s="8" t="s">
-        <v>881</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>882</v>
-      </c>
-      <c r="R22" s="8" t="s">
-        <v>883</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
+        <v>880</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>881</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>882</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>883</v>
+      </c>
+      <c r="E23" s="8" t="s">
         <v>884</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="F23" s="8" t="s">
         <v>885</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="G23" s="8" t="s">
         <v>886</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="H23" s="8" t="s">
         <v>887</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="I23" s="8" t="s">
         <v>888</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="J23" s="8" t="s">
         <v>889</v>
       </c>
-      <c r="G23" s="8" t="s">
+      <c r="K23" s="8" t="s">
         <v>890</v>
       </c>
-      <c r="H23" s="8" t="s">
+      <c r="L23" s="8" t="s">
         <v>891</v>
       </c>
-      <c r="I23" s="8" t="s">
+      <c r="M23" s="8" t="s">
         <v>892</v>
       </c>
-      <c r="J23" s="8" t="s">
+      <c r="N23" s="8" t="s">
         <v>893</v>
       </c>
-      <c r="K23" s="8" t="s">
+      <c r="O23" s="8" t="s">
         <v>894</v>
       </c>
-      <c r="L23" s="8" t="s">
+      <c r="P23" s="8" t="s">
         <v>895</v>
       </c>
-      <c r="M23" s="3" t="s">
+      <c r="Q23" s="3" t="s">
         <v>896</v>
       </c>
-      <c r="N23" s="8" t="s">
+      <c r="R23" s="8" t="s">
         <v>897</v>
-      </c>
-      <c r="O23" s="8" t="s">
-        <v>898</v>
-      </c>
-      <c r="P23" s="8" t="s">
-        <v>899</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>900</v>
-      </c>
-      <c r="R23" s="8" t="s">
-        <v>901</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
+        <v>898</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>899</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>900</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>901</v>
+      </c>
+      <c r="E24" s="8" t="s">
         <v>902</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="F24" s="8" t="s">
         <v>903</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="G24" s="8" t="s">
         <v>904</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="H24" s="8" t="s">
         <v>905</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="I24" s="8" t="s">
         <v>906</v>
       </c>
-      <c r="F24" s="8" t="s">
+      <c r="J24" s="8" t="s">
         <v>907</v>
       </c>
-      <c r="G24" s="8" t="s">
+      <c r="K24" s="8" t="s">
         <v>908</v>
       </c>
-      <c r="H24" s="8" t="s">
+      <c r="L24" s="8" t="s">
         <v>909</v>
       </c>
-      <c r="I24" s="8" t="s">
+      <c r="M24" s="8" t="s">
         <v>910</v>
       </c>
-      <c r="J24" s="8" t="s">
+      <c r="N24" s="8" t="s">
         <v>911</v>
       </c>
-      <c r="K24" s="8" t="s">
+      <c r="O24" s="8" t="s">
         <v>912</v>
       </c>
-      <c r="L24" s="8" t="s">
+      <c r="P24" s="8" t="s">
         <v>913</v>
       </c>
-      <c r="M24" s="3" t="s">
+      <c r="Q24" s="3" t="s">
         <v>914</v>
       </c>
-      <c r="N24" s="8" t="s">
+      <c r="R24" s="8" t="s">
         <v>915</v>
-      </c>
-      <c r="O24" s="8" t="s">
-        <v>916</v>
-      </c>
-      <c r="P24" s="8" t="s">
-        <v>917</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>918</v>
-      </c>
-      <c r="R24" s="8" t="s">
-        <v>919</v>
       </c>
     </row>
   </sheetData>
@@ -16862,25 +16871,25 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>916</v>
+      </c>
+      <c r="C1" t="s">
+        <v>917</v>
+      </c>
+      <c r="D1" t="s">
+        <v>918</v>
+      </c>
+      <c r="E1" t="s">
+        <v>919</v>
+      </c>
+      <c r="F1" t="s">
         <v>920</v>
       </c>
-      <c r="C1" t="s">
+      <c r="G1" t="s">
         <v>921</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" t="s">
         <v>922</v>
-      </c>
-      <c r="E1" t="s">
-        <v>923</v>
-      </c>
-      <c r="F1" t="s">
-        <v>924</v>
-      </c>
-      <c r="G1" t="s">
-        <v>925</v>
-      </c>
-      <c r="H1" t="s">
-        <v>926</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -16888,13 +16897,13 @@
         <v>234</v>
       </c>
       <c r="B2" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="C2" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="D2" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="E2">
         <v>100000000</v>
@@ -16903,7 +16912,7 @@
         <v>2575000000</v>
       </c>
       <c r="G2" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -16914,13 +16923,13 @@
         <v>44</v>
       </c>
       <c r="B3" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
       <c r="C3" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="D3" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="E3">
         <v>100000000</v>
@@ -16929,7 +16938,7 @@
         <v>211000000</v>
       </c>
       <c r="G3" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -16943,10 +16952,10 @@
         <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
       <c r="D4" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
       <c r="E4">
         <v>100000000</v>
@@ -16955,7 +16964,7 @@
         <v>810000000</v>
       </c>
       <c r="G4" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="H4">
         <v>3</v>
@@ -16966,13 +16975,13 @@
         <v>224</v>
       </c>
       <c r="B5" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="C5" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="D5" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="E5">
         <v>100000000</v>
@@ -16981,7 +16990,7 @@
         <v>2569000000</v>
       </c>
       <c r="G5" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
       <c r="H5">
         <v>4</v>
@@ -16992,13 +17001,13 @@
         <v>499</v>
       </c>
       <c r="B6" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="C6" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="D6" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="E6">
         <v>100000000</v>
@@ -17007,7 +17016,7 @@
         <v>759000000</v>
       </c>
       <c r="G6" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="H6">
         <v>5</v>
@@ -17018,13 +17027,13 @@
         <v>500</v>
       </c>
       <c r="B7" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="C7" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
       <c r="D7" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="E7">
         <v>100000000</v>
@@ -17033,7 +17042,7 @@
         <v>280000000</v>
       </c>
       <c r="G7" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="H7">
         <v>6</v>
@@ -17044,13 +17053,13 @@
         <v>229</v>
       </c>
       <c r="B8" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="C8" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
       <c r="D8" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="E8">
         <v>100000000</v>
@@ -17059,7 +17068,7 @@
         <v>2154000000</v>
       </c>
       <c r="G8" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="H8">
         <v>7</v>
@@ -17070,13 +17079,13 @@
         <v>501</v>
       </c>
       <c r="B9" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="C9" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="D9" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
       <c r="E9">
         <v>100000000</v>
@@ -17085,7 +17094,7 @@
         <v>223000000</v>
       </c>
       <c r="G9" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
       <c r="H9">
         <v>8</v>
@@ -17096,13 +17105,13 @@
         <v>502</v>
       </c>
       <c r="B10" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="C10" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="D10" t="s">
-        <v>960</v>
+        <v>956</v>
       </c>
       <c r="E10">
         <v>100000000</v>
@@ -17111,7 +17120,7 @@
         <v>11000000</v>
       </c>
       <c r="G10" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="H10">
         <v>9</v>
@@ -17122,13 +17131,13 @@
         <v>49</v>
       </c>
       <c r="B11" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="C11" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="D11" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="E11">
         <v>100000000</v>
@@ -17137,7 +17146,7 @@
         <v>119000000</v>
       </c>
       <c r="G11" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="H11">
         <v>10</v>
@@ -17148,13 +17157,13 @@
         <v>233</v>
       </c>
       <c r="B12" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
       <c r="C12" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="D12" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="E12">
         <v>100000000</v>
@@ -17163,7 +17172,7 @@
         <v>2121000000</v>
       </c>
       <c r="G12" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="H12">
         <v>11</v>
@@ -17174,13 +17183,13 @@
         <v>238</v>
       </c>
       <c r="B13" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="C13" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="D13" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="E13">
         <v>100000000</v>
@@ -17189,7 +17198,7 @@
         <v>300000000</v>
       </c>
       <c r="G13" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="H13">
         <v>12</v>
@@ -17200,13 +17209,13 @@
         <v>38</v>
       </c>
       <c r="B14" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="C14" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="D14" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
       <c r="E14">
         <v>100000000</v>
@@ -17215,7 +17224,7 @@
         <v>300000000</v>
       </c>
       <c r="G14" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
       <c r="H14">
         <v>13</v>
@@ -17226,13 +17235,13 @@
         <v>498</v>
       </c>
       <c r="B15" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="C15" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="D15" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="E15">
         <v>100000000</v>
@@ -17241,7 +17250,7 @@
         <v>357000000</v>
       </c>
       <c r="G15" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
       <c r="H15">
         <v>14</v>
@@ -17252,13 +17261,13 @@
         <v>497</v>
       </c>
       <c r="B16" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
       <c r="C16" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="D16" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="E16">
         <v>100000000</v>
@@ -17267,7 +17276,7 @@
         <v>137000000</v>
       </c>
       <c r="G16" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="H16">
         <v>15</v>
@@ -17278,13 +17287,13 @@
         <v>225</v>
       </c>
       <c r="B17" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
       <c r="C17" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="D17" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="E17">
         <v>100000000</v>
@@ -17293,7 +17302,7 @@
         <v>440000000</v>
       </c>
       <c r="G17" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="H17">
         <v>16</v>
@@ -17304,13 +17313,13 @@
         <v>504</v>
       </c>
       <c r="B18" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="C18" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="D18" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
       <c r="E18">
         <v>100000000</v>
@@ -17319,7 +17328,7 @@
         <v>181000000</v>
       </c>
       <c r="G18" t="s">
-        <v>992</v>
+        <v>988</v>
       </c>
       <c r="H18">
         <v>17</v>
@@ -17330,13 +17339,13 @@
         <v>505</v>
       </c>
       <c r="B19" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="C19" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
       <c r="D19" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="E19">
         <v>100000000</v>
@@ -17345,7 +17354,7 @@
         <v>210000000</v>
       </c>
       <c r="G19" t="s">
-        <v>996</v>
+        <v>992</v>
       </c>
     </row>
   </sheetData>

--- a/LMI Base.xlsx
+++ b/LMI Base.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEC00D50-E9E0-49E6-BDBA-40F1A959C766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro Liga" sheetId="1" r:id="rId1"/>

--- a/LMI Base.xlsx
+++ b/LMI Base.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEC00D50-E9E0-49E6-BDBA-40F1A959C766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8057D647-6815-467E-95F5-0C7119D1CAC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro Liga" sheetId="1" r:id="rId1"/>
@@ -101,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2555" uniqueCount="1087">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2565" uniqueCount="1087">
   <si>
     <t>Equipo</t>
   </si>
@@ -3438,7 +3438,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3467,6 +3467,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -8991,7 +8994,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86FCEC72-F57A-476F-86FC-E29836F3A0C3}">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.21875" customWidth="1"/>
@@ -9291,7 +9294,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>259</v>
       </c>
@@ -9305,7 +9308,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C18" s="8" t="s">
         <v>583</v>
       </c>
@@ -9315,8 +9318,17 @@
       <c r="E18" s="6">
         <v>103</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G18" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>993</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C19" s="8" t="s">
         <v>833</v>
       </c>
@@ -9325,6 +9337,37 @@
       </c>
       <c r="E19" s="6">
         <v>105</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>901</v>
+      </c>
+      <c r="H19" s="12" t="s">
+        <v>1077</v>
+      </c>
+      <c r="I19">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C21" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>993</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C22" s="8" t="s">
+        <v>701</v>
+      </c>
+      <c r="D22" t="s">
+        <v>1077</v>
+      </c>
+      <c r="E22">
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/LMI Base.xlsx
+++ b/LMI Base.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8057D647-6815-467E-95F5-0C7119D1CAC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D21C11C4-3329-497D-8B86-05F1783BD993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro Liga" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">Mercado!$A$1:$G$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Registro Champions'!$A$1:$D$122</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Registro Liga'!$A$1:$D$251</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">RegistroEstelar!$A$1:$D$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">RegistroEstelar!$A$1:$D$83</definedName>
     <definedName name="AC_Milan">BD!$D$2:$D$24</definedName>
     <definedName name="AC_Milán">Lista!$E$2:$E$1048576</definedName>
     <definedName name="AcMilan">Lista!$E$2:$E$1048576</definedName>
@@ -101,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2565" uniqueCount="1087">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2573" uniqueCount="1087">
   <si>
     <t>Equipo</t>
   </si>
@@ -3438,7 +3438,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3467,9 +3467,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -9341,7 +9338,7 @@
       <c r="G19" s="8" t="s">
         <v>901</v>
       </c>
-      <c r="H19" s="12" t="s">
+      <c r="H19" s="1" t="s">
         <v>1077</v>
       </c>
       <c r="I19">
@@ -12163,7 +12160,7 @@
         <v>301</v>
       </c>
       <c r="C6" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="6">
         <v>3</v>
@@ -12281,7 +12278,7 @@
         <v>27</v>
       </c>
       <c r="C15" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D15" s="6">
         <v>1</v>
@@ -12298,7 +12295,7 @@
         <v>5</v>
       </c>
       <c r="D16" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -12379,7 +12376,7 @@
         <v>197</v>
       </c>
       <c r="C22" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D22" s="6">
         <v>1</v>
@@ -13106,28 +13103,52 @@
       <c r="D81" s="6"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A82" s="6"/>
-      <c r="B82" s="6"/>
-      <c r="C82" s="6"/>
+      <c r="A82" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="C82" s="6">
+        <v>2</v>
+      </c>
       <c r="D82" s="6"/>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A83" s="6"/>
-      <c r="B83" s="6"/>
+      <c r="A83" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>436</v>
+      </c>
       <c r="C83" s="6"/>
-      <c r="D83" s="6"/>
+      <c r="D83" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A84" s="6"/>
-      <c r="B84" s="6"/>
-      <c r="C84" s="6"/>
+      <c r="A84" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C84" s="6">
+        <v>1</v>
+      </c>
       <c r="D84" s="6"/>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A85" s="6"/>
-      <c r="B85" s="6"/>
+      <c r="A85" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>338</v>
+      </c>
       <c r="C85" s="6"/>
-      <c r="D85" s="6"/>
+      <c r="D85" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="6"/>
@@ -14120,7 +14141,7 @@
       <c r="D250" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D80" xr:uid="{00000000-0009-0000-0000-000004000000}">
+  <autoFilter ref="A1:D83" xr:uid="{00000000-0009-0000-0000-000004000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D81">
       <sortCondition descending="1" ref="D1:D80"/>
     </sortState>

--- a/LMI Base.xlsx
+++ b/LMI Base.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D21C11C4-3329-497D-8B86-05F1783BD993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{694B9FA3-1AD7-4213-B995-1FE019DFAE23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro Liga" sheetId="1" r:id="rId1"/>
@@ -2716,9 +2716,6 @@
     <t>MP Azzedine Ounahi</t>
   </si>
   <si>
-    <t>DC Tammy Abraham</t>
-  </si>
-  <si>
     <t>ED Francisco Trincão</t>
   </si>
   <si>
@@ -3362,6 +3359,9 @@
   </si>
   <si>
     <t>ID Phil Foden (P)</t>
+  </si>
+  <si>
+    <t>PT Jan Oblak</t>
   </si>
 </sst>
 </file>
@@ -7163,22 +7163,22 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
+        <v>992</v>
+      </c>
+      <c r="C1" t="s">
         <v>993</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>994</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>995</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>996</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>997</v>
-      </c>
-      <c r="G1" t="s">
-        <v>998</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -7186,30 +7186,30 @@
         <v>464</v>
       </c>
       <c r="B2" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="C2" t="s">
         <v>229</v>
       </c>
       <c r="D2" t="s">
+        <v>999</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
         <v>1000</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2" t="s">
-        <v>1001</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B3" t="s">
+        <v>998</v>
+      </c>
+      <c r="C3" t="s">
         <v>999</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1000</v>
       </c>
       <c r="D3" t="s">
         <v>229</v>
@@ -7218,7 +7218,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -7226,7 +7226,7 @@
         <v>57</v>
       </c>
       <c r="B4" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="C4" t="s">
         <v>234</v>
@@ -7238,7 +7238,7 @@
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -7246,7 +7246,7 @@
         <v>66</v>
       </c>
       <c r="B5" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="C5" t="s">
         <v>55</v>
@@ -7258,15 +7258,15 @@
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B6" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="C6" t="s">
         <v>501</v>
@@ -7281,7 +7281,7 @@
         <v>2</v>
       </c>
       <c r="G6" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -7289,7 +7289,7 @@
         <v>267</v>
       </c>
       <c r="B7" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="C7" t="s">
         <v>501</v>
@@ -7304,15 +7304,15 @@
         <v>2</v>
       </c>
       <c r="G7" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B8" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="C8" t="s">
         <v>234</v>
@@ -7327,15 +7327,15 @@
         <v>2</v>
       </c>
       <c r="G8" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B9" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="C9" t="s">
         <v>229</v>
@@ -7350,15 +7350,15 @@
         <v>2</v>
       </c>
       <c r="G9" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B10" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="C10" t="s">
         <v>233</v>
@@ -7373,7 +7373,7 @@
         <v>2</v>
       </c>
       <c r="G10" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -7381,10 +7381,10 @@
         <v>157</v>
       </c>
       <c r="B11" t="s">
+        <v>998</v>
+      </c>
+      <c r="C11" t="s">
         <v>999</v>
-      </c>
-      <c r="C11" t="s">
-        <v>1000</v>
       </c>
       <c r="D11" t="s">
         <v>234</v>
@@ -7396,21 +7396,21 @@
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B12" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="C12" t="s">
         <v>229</v>
       </c>
       <c r="D12" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -7419,7 +7419,7 @@
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -7427,10 +7427,10 @@
         <v>184</v>
       </c>
       <c r="B13" t="s">
+        <v>998</v>
+      </c>
+      <c r="C13" t="s">
         <v>999</v>
-      </c>
-      <c r="C13" t="s">
-        <v>1000</v>
       </c>
       <c r="D13" t="s">
         <v>229</v>
@@ -7442,7 +7442,7 @@
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
   </sheetData>
@@ -7458,21 +7458,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B1" t="s">
         <v>1009</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1010</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1011</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B2" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -7480,10 +7480,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B3" t="s">
         <v>1012</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1013</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -7491,10 +7491,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B4" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -7502,10 +7502,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B5" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -7513,10 +7513,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B6" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -7524,10 +7524,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B7" t="s">
         <v>1016</v>
-      </c>
-      <c r="B7" t="s">
-        <v>1017</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -7535,10 +7535,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B8" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -7546,10 +7546,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B9" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -7557,10 +7557,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B10" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -7568,10 +7568,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B11" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -7579,10 +7579,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B12" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -7590,10 +7590,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B13" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -7601,10 +7601,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B14" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -7716,7 +7716,7 @@
         <v>265</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>267</v>
@@ -7737,7 +7737,7 @@
         <v>272</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>274</v>
@@ -7757,10 +7757,10 @@
         <v>277</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>1022</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>1023</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>279</v>
@@ -7813,13 +7813,13 @@
         <v>289</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>1024</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>1025</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>1026</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>292</v>
@@ -7828,7 +7828,7 @@
         <v>293</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>294</v>
@@ -7881,7 +7881,7 @@
         <v>306</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>326</v>
@@ -7905,7 +7905,7 @@
         <v>313</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>176</v>
@@ -7925,10 +7925,10 @@
         <v>316</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>1030</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>1031</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>317</v>
@@ -7964,7 +7964,7 @@
         <v>129</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="P6" s="3" t="s">
         <v>118</v>
@@ -8017,7 +8017,7 @@
         <v>330</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="O7" s="3" t="s">
         <v>167</v>
@@ -8040,7 +8040,7 @@
         <v>249</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>191</v>
@@ -8067,7 +8067,7 @@
         <v>169</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>131</v>
@@ -8146,13 +8146,13 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>140</v>
@@ -8188,7 +8188,7 @@
         <v>57</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="P10" s="3" t="s">
         <v>155</v>
@@ -8261,7 +8261,7 @@
         <v>54</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>192</v>
@@ -8273,10 +8273,10 @@
         <v>53</v>
       </c>
       <c r="F12" s="3" t="s">
+        <v>1039</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>1040</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>1041</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>82</v>
@@ -8314,7 +8314,7 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>440</v>
@@ -8332,7 +8332,7 @@
         <v>84</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>370</v>
@@ -8347,7 +8347,7 @@
         <v>372</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="M13" s="3" t="s">
         <v>374</v>
@@ -8359,7 +8359,7 @@
         <v>376</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="Q13" s="3" t="s">
         <v>377</v>
@@ -8370,13 +8370,13 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>211</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>380</v>
@@ -8385,10 +8385,10 @@
         <v>381</v>
       </c>
       <c r="F14" s="3" t="s">
+        <v>1047</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>1048</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>1049</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>382</v>
@@ -8409,10 +8409,10 @@
         <v>387</v>
       </c>
       <c r="N14" s="3" t="s">
+        <v>1049</v>
+      </c>
+      <c r="O14" s="3" t="s">
         <v>1050</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>1051</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>390</v>
@@ -8426,13 +8426,13 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>369</v>
@@ -8488,7 +8488,7 @@
         <v>189</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>106</v>
@@ -8500,7 +8500,7 @@
         <v>114</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>410</v>
@@ -8515,7 +8515,7 @@
         <v>412</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>157</v>
@@ -8527,7 +8527,7 @@
         <v>404</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="Q16" s="3" t="s">
         <v>257</v>
@@ -8553,7 +8553,7 @@
         <v>420</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>205</v>
@@ -8571,7 +8571,7 @@
         <v>424</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>425</v>
@@ -8597,7 +8597,7 @@
         <v>431</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>246</v>
@@ -8612,7 +8612,7 @@
         <v>175</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>435</v>
@@ -8653,7 +8653,7 @@
         <v>470</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>117</v>
@@ -8668,7 +8668,7 @@
         <v>170</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>444</v>
@@ -8695,7 +8695,7 @@
         <v>73</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="Q19" s="3" t="s">
         <v>450</v>
@@ -8709,7 +8709,7 @@
         <v>135</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>202</v>
@@ -8765,7 +8765,7 @@
         <v>22</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>178</v>
@@ -8780,7 +8780,7 @@
         <v>460</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>461</v>
@@ -8807,7 +8807,7 @@
         <v>187</v>
       </c>
       <c r="P21" s="3" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>196</v>
@@ -8824,16 +8824,16 @@
         <v>477</v>
       </c>
       <c r="C22" s="5" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D22" s="5" t="s">
         <v>1069</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>1070</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>152</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>204</v>
@@ -8874,7 +8874,7 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>141</v>
@@ -8901,7 +8901,7 @@
         <v>64</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>39</v>
@@ -8933,10 +8933,10 @@
         <v>486</v>
       </c>
       <c r="B24" s="5" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>1074</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>1075</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>46</v>
@@ -9011,19 +9011,19 @@
         <v>20</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>51</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="K1" s="5"/>
     </row>
@@ -9035,7 +9035,7 @@
         <v>595</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="E2" s="3">
         <v>103</v>
@@ -9044,7 +9044,7 @@
         <v>688</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="I2" s="6">
         <v>101</v>
@@ -9063,19 +9063,19 @@
         <v>32</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>44</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -9086,7 +9086,7 @@
         <v>615</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="E5" s="6">
         <v>107</v>
@@ -9095,7 +9095,7 @@
         <v>610</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="I5" s="6">
         <v>101</v>
@@ -9114,19 +9114,19 @@
         <v>55</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>119</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
@@ -9134,10 +9134,10 @@
         <v>36</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="E8" s="6">
         <v>102</v>
@@ -9146,7 +9146,7 @@
         <v>696</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="I8" s="6">
         <v>106</v>
@@ -9160,7 +9160,7 @@
         <v>643</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="I9" s="6">
         <v>103</v>
@@ -9174,16 +9174,16 @@
         <v>49</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>589</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="I10" s="6">
         <v>102</v>
@@ -9197,7 +9197,7 @@
         <v>618</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="E11" s="6">
         <v>104</v>
@@ -9211,10 +9211,10 @@
         <v>36</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -9225,16 +9225,16 @@
         <v>26</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="E13" s="3" t="s">
+        <v>1075</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>904</v>
+      </c>
+      <c r="H13" s="3" t="s">
         <v>1076</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>905</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>1077</v>
       </c>
       <c r="I13" s="6">
         <v>107</v>
@@ -9248,7 +9248,7 @@
         <v>552</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="E14" s="6">
         <v>106</v>
@@ -9262,7 +9262,7 @@
         <v>570</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="E15" s="6">
         <v>105</v>
@@ -9271,10 +9271,10 @@
         <v>193</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
@@ -9282,10 +9282,10 @@
         <v>193</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="I16" s="6">
         <v>105</v>
@@ -9299,10 +9299,10 @@
         <v>69</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
@@ -9310,7 +9310,7 @@
         <v>583</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="E18" s="6">
         <v>103</v>
@@ -9319,10 +9319,10 @@
         <v>17</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
@@ -9330,16 +9330,16 @@
         <v>833</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="E19" s="6">
         <v>105</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="I19">
         <v>104</v>
@@ -9350,10 +9350,10 @@
         <v>259</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
@@ -9361,7 +9361,7 @@
         <v>701</v>
       </c>
       <c r="D22" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="E22">
         <v>101</v>
@@ -14735,7 +14735,7 @@
         <v>355</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>57</v>
@@ -15183,7 +15183,7 @@
         <v>436</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>105</v>
@@ -15351,7 +15351,7 @@
         <v>162</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>465</v>
@@ -15717,7 +15717,7 @@
         <v>535</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="N3" s="8" t="s">
         <v>536</v>
@@ -16109,7 +16109,7 @@
         <v>660</v>
       </c>
       <c r="M10" s="8" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="N10" s="8" t="s">
         <v>661</v>
@@ -16557,7 +16557,7 @@
         <v>802</v>
       </c>
       <c r="M18" s="8" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="N18" s="8" t="s">
         <v>804</v>
@@ -16725,7 +16725,7 @@
         <v>856</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="N21" s="8" t="s">
         <v>857</v>
@@ -16772,143 +16772,143 @@
         <v>870</v>
       </c>
       <c r="J22" s="8" t="s">
+        <v>1086</v>
+      </c>
+      <c r="K22" s="8" t="s">
         <v>871</v>
       </c>
-      <c r="K22" s="8" t="s">
+      <c r="L22" s="8" t="s">
         <v>872</v>
       </c>
-      <c r="L22" s="8" t="s">
+      <c r="M22" s="8" t="s">
         <v>873</v>
       </c>
-      <c r="M22" s="8" t="s">
+      <c r="N22" s="8" t="s">
         <v>874</v>
       </c>
-      <c r="N22" s="8" t="s">
+      <c r="O22" s="8" t="s">
         <v>875</v>
       </c>
-      <c r="O22" s="8" t="s">
+      <c r="P22" s="8" t="s">
         <v>876</v>
       </c>
-      <c r="P22" s="8" t="s">
+      <c r="Q22" s="3" t="s">
         <v>877</v>
       </c>
-      <c r="Q22" s="3" t="s">
+      <c r="R22" s="8" t="s">
         <v>878</v>
-      </c>
-      <c r="R22" s="8" t="s">
-        <v>879</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
+        <v>879</v>
+      </c>
+      <c r="B23" s="8" t="s">
         <v>880</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="C23" s="8" t="s">
         <v>881</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="D23" s="8" t="s">
         <v>882</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="E23" s="8" t="s">
         <v>883</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="F23" s="8" t="s">
         <v>884</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="G23" s="8" t="s">
         <v>885</v>
       </c>
-      <c r="G23" s="8" t="s">
+      <c r="H23" s="8" t="s">
         <v>886</v>
       </c>
-      <c r="H23" s="8" t="s">
+      <c r="I23" s="8" t="s">
         <v>887</v>
       </c>
-      <c r="I23" s="8" t="s">
+      <c r="J23" s="8" t="s">
         <v>888</v>
       </c>
-      <c r="J23" s="8" t="s">
+      <c r="K23" s="8" t="s">
         <v>889</v>
       </c>
-      <c r="K23" s="8" t="s">
+      <c r="L23" s="8" t="s">
         <v>890</v>
       </c>
-      <c r="L23" s="8" t="s">
+      <c r="M23" s="8" t="s">
         <v>891</v>
       </c>
-      <c r="M23" s="8" t="s">
+      <c r="N23" s="8" t="s">
         <v>892</v>
       </c>
-      <c r="N23" s="8" t="s">
+      <c r="O23" s="8" t="s">
         <v>893</v>
       </c>
-      <c r="O23" s="8" t="s">
+      <c r="P23" s="8" t="s">
         <v>894</v>
       </c>
-      <c r="P23" s="8" t="s">
+      <c r="Q23" s="3" t="s">
         <v>895</v>
       </c>
-      <c r="Q23" s="3" t="s">
+      <c r="R23" s="8" t="s">
         <v>896</v>
-      </c>
-      <c r="R23" s="8" t="s">
-        <v>897</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
+        <v>897</v>
+      </c>
+      <c r="B24" s="8" t="s">
         <v>898</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="C24" s="8" t="s">
         <v>899</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="D24" s="8" t="s">
         <v>900</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="E24" s="8" t="s">
         <v>901</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="F24" s="8" t="s">
         <v>902</v>
       </c>
-      <c r="F24" s="8" t="s">
+      <c r="G24" s="8" t="s">
         <v>903</v>
       </c>
-      <c r="G24" s="8" t="s">
+      <c r="H24" s="8" t="s">
         <v>904</v>
       </c>
-      <c r="H24" s="8" t="s">
+      <c r="I24" s="8" t="s">
         <v>905</v>
       </c>
-      <c r="I24" s="8" t="s">
+      <c r="J24" s="8" t="s">
         <v>906</v>
       </c>
-      <c r="J24" s="8" t="s">
+      <c r="K24" s="8" t="s">
         <v>907</v>
       </c>
-      <c r="K24" s="8" t="s">
+      <c r="L24" s="8" t="s">
         <v>908</v>
       </c>
-      <c r="L24" s="8" t="s">
+      <c r="M24" s="8" t="s">
         <v>909</v>
       </c>
-      <c r="M24" s="8" t="s">
+      <c r="N24" s="8" t="s">
         <v>910</v>
       </c>
-      <c r="N24" s="8" t="s">
+      <c r="O24" s="8" t="s">
         <v>911</v>
       </c>
-      <c r="O24" s="8" t="s">
+      <c r="P24" s="8" t="s">
         <v>912</v>
       </c>
-      <c r="P24" s="8" t="s">
+      <c r="Q24" s="3" t="s">
         <v>913</v>
       </c>
-      <c r="Q24" s="3" t="s">
+      <c r="R24" s="8" t="s">
         <v>914</v>
-      </c>
-      <c r="R24" s="8" t="s">
-        <v>915</v>
       </c>
     </row>
   </sheetData>
@@ -16935,25 +16935,25 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>915</v>
+      </c>
+      <c r="C1" t="s">
         <v>916</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>917</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>918</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>919</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>920</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>921</v>
-      </c>
-      <c r="H1" t="s">
-        <v>922</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -16961,13 +16961,13 @@
         <v>234</v>
       </c>
       <c r="B2" t="s">
+        <v>922</v>
+      </c>
+      <c r="C2" t="s">
         <v>923</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>924</v>
-      </c>
-      <c r="D2" t="s">
-        <v>925</v>
       </c>
       <c r="E2">
         <v>100000000</v>
@@ -16976,7 +16976,7 @@
         <v>2575000000</v>
       </c>
       <c r="G2" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -16987,13 +16987,13 @@
         <v>44</v>
       </c>
       <c r="B3" t="s">
+        <v>926</v>
+      </c>
+      <c r="C3" t="s">
         <v>927</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>928</v>
-      </c>
-      <c r="D3" t="s">
-        <v>929</v>
       </c>
       <c r="E3">
         <v>100000000</v>
@@ -17002,7 +17002,7 @@
         <v>211000000</v>
       </c>
       <c r="G3" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -17016,10 +17016,10 @@
         <v>55</v>
       </c>
       <c r="C4" t="s">
+        <v>930</v>
+      </c>
+      <c r="D4" t="s">
         <v>931</v>
-      </c>
-      <c r="D4" t="s">
-        <v>932</v>
       </c>
       <c r="E4">
         <v>100000000</v>
@@ -17028,7 +17028,7 @@
         <v>810000000</v>
       </c>
       <c r="G4" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H4">
         <v>3</v>
@@ -17039,13 +17039,13 @@
         <v>224</v>
       </c>
       <c r="B5" t="s">
+        <v>933</v>
+      </c>
+      <c r="C5" t="s">
         <v>934</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>935</v>
-      </c>
-      <c r="D5" t="s">
-        <v>936</v>
       </c>
       <c r="E5">
         <v>100000000</v>
@@ -17054,7 +17054,7 @@
         <v>2569000000</v>
       </c>
       <c r="G5" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="H5">
         <v>4</v>
@@ -17065,13 +17065,13 @@
         <v>499</v>
       </c>
       <c r="B6" t="s">
+        <v>937</v>
+      </c>
+      <c r="C6" t="s">
         <v>938</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>939</v>
-      </c>
-      <c r="D6" t="s">
-        <v>940</v>
       </c>
       <c r="E6">
         <v>100000000</v>
@@ -17080,7 +17080,7 @@
         <v>759000000</v>
       </c>
       <c r="G6" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H6">
         <v>5</v>
@@ -17091,13 +17091,13 @@
         <v>500</v>
       </c>
       <c r="B7" t="s">
+        <v>941</v>
+      </c>
+      <c r="C7" t="s">
         <v>942</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>943</v>
-      </c>
-      <c r="D7" t="s">
-        <v>944</v>
       </c>
       <c r="E7">
         <v>100000000</v>
@@ -17106,7 +17106,7 @@
         <v>280000000</v>
       </c>
       <c r="G7" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H7">
         <v>6</v>
@@ -17117,13 +17117,13 @@
         <v>229</v>
       </c>
       <c r="B8" t="s">
+        <v>945</v>
+      </c>
+      <c r="C8" t="s">
         <v>946</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>947</v>
-      </c>
-      <c r="D8" t="s">
-        <v>948</v>
       </c>
       <c r="E8">
         <v>100000000</v>
@@ -17132,7 +17132,7 @@
         <v>2154000000</v>
       </c>
       <c r="G8" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H8">
         <v>7</v>
@@ -17143,13 +17143,13 @@
         <v>501</v>
       </c>
       <c r="B9" t="s">
+        <v>949</v>
+      </c>
+      <c r="C9" t="s">
         <v>950</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>951</v>
-      </c>
-      <c r="D9" t="s">
-        <v>952</v>
       </c>
       <c r="E9">
         <v>100000000</v>
@@ -17158,7 +17158,7 @@
         <v>223000000</v>
       </c>
       <c r="G9" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H9">
         <v>8</v>
@@ -17169,13 +17169,13 @@
         <v>502</v>
       </c>
       <c r="B10" t="s">
+        <v>953</v>
+      </c>
+      <c r="C10" t="s">
         <v>954</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>955</v>
-      </c>
-      <c r="D10" t="s">
-        <v>956</v>
       </c>
       <c r="E10">
         <v>100000000</v>
@@ -17184,7 +17184,7 @@
         <v>11000000</v>
       </c>
       <c r="G10" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H10">
         <v>9</v>
@@ -17195,13 +17195,13 @@
         <v>49</v>
       </c>
       <c r="B11" t="s">
+        <v>957</v>
+      </c>
+      <c r="C11" t="s">
         <v>958</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>959</v>
-      </c>
-      <c r="D11" t="s">
-        <v>960</v>
       </c>
       <c r="E11">
         <v>100000000</v>
@@ -17210,7 +17210,7 @@
         <v>119000000</v>
       </c>
       <c r="G11" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H11">
         <v>10</v>
@@ -17221,13 +17221,13 @@
         <v>233</v>
       </c>
       <c r="B12" t="s">
+        <v>961</v>
+      </c>
+      <c r="C12" t="s">
         <v>962</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>963</v>
-      </c>
-      <c r="D12" t="s">
-        <v>964</v>
       </c>
       <c r="E12">
         <v>100000000</v>
@@ -17236,7 +17236,7 @@
         <v>2121000000</v>
       </c>
       <c r="G12" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H12">
         <v>11</v>
@@ -17247,13 +17247,13 @@
         <v>238</v>
       </c>
       <c r="B13" t="s">
+        <v>965</v>
+      </c>
+      <c r="C13" t="s">
         <v>966</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>967</v>
-      </c>
-      <c r="D13" t="s">
-        <v>968</v>
       </c>
       <c r="E13">
         <v>100000000</v>
@@ -17262,7 +17262,7 @@
         <v>300000000</v>
       </c>
       <c r="G13" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="H13">
         <v>12</v>
@@ -17273,13 +17273,13 @@
         <v>38</v>
       </c>
       <c r="B14" t="s">
+        <v>969</v>
+      </c>
+      <c r="C14" t="s">
         <v>970</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>971</v>
-      </c>
-      <c r="D14" t="s">
-        <v>972</v>
       </c>
       <c r="E14">
         <v>100000000</v>
@@ -17288,7 +17288,7 @@
         <v>300000000</v>
       </c>
       <c r="G14" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="H14">
         <v>13</v>
@@ -17299,13 +17299,13 @@
         <v>498</v>
       </c>
       <c r="B15" t="s">
+        <v>973</v>
+      </c>
+      <c r="C15" t="s">
         <v>974</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>975</v>
-      </c>
-      <c r="D15" t="s">
-        <v>976</v>
       </c>
       <c r="E15">
         <v>100000000</v>
@@ -17314,7 +17314,7 @@
         <v>357000000</v>
       </c>
       <c r="G15" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H15">
         <v>14</v>
@@ -17325,13 +17325,13 @@
         <v>497</v>
       </c>
       <c r="B16" t="s">
+        <v>977</v>
+      </c>
+      <c r="C16" t="s">
         <v>978</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>979</v>
-      </c>
-      <c r="D16" t="s">
-        <v>980</v>
       </c>
       <c r="E16">
         <v>100000000</v>
@@ -17340,7 +17340,7 @@
         <v>137000000</v>
       </c>
       <c r="G16" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="H16">
         <v>15</v>
@@ -17351,13 +17351,13 @@
         <v>225</v>
       </c>
       <c r="B17" t="s">
+        <v>981</v>
+      </c>
+      <c r="C17" t="s">
+        <v>962</v>
+      </c>
+      <c r="D17" t="s">
         <v>982</v>
-      </c>
-      <c r="C17" t="s">
-        <v>963</v>
-      </c>
-      <c r="D17" t="s">
-        <v>983</v>
       </c>
       <c r="E17">
         <v>100000000</v>
@@ -17366,7 +17366,7 @@
         <v>440000000</v>
       </c>
       <c r="G17" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="H17">
         <v>16</v>
@@ -17377,13 +17377,13 @@
         <v>504</v>
       </c>
       <c r="B18" t="s">
+        <v>984</v>
+      </c>
+      <c r="C18" t="s">
         <v>985</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>986</v>
-      </c>
-      <c r="D18" t="s">
-        <v>987</v>
       </c>
       <c r="E18">
         <v>100000000</v>
@@ -17392,7 +17392,7 @@
         <v>181000000</v>
       </c>
       <c r="G18" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="H18">
         <v>17</v>
@@ -17403,13 +17403,13 @@
         <v>505</v>
       </c>
       <c r="B19" t="s">
+        <v>988</v>
+      </c>
+      <c r="C19" t="s">
         <v>989</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>990</v>
-      </c>
-      <c r="D19" t="s">
-        <v>991</v>
       </c>
       <c r="E19">
         <v>100000000</v>
@@ -17418,7 +17418,7 @@
         <v>210000000</v>
       </c>
       <c r="G19" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
   </sheetData>

--- a/LMI Base.xlsx
+++ b/LMI Base.xlsx
@@ -581,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E247"/>
+  <dimension ref="A1:D247"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col width="16.88671875" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -13790,7 +13790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:R24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col width="17.77734375" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
@@ -13899,6 +13899,11 @@
           <t>Club_America</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Club_Atlético_River_Plate</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -13986,6 +13991,11 @@
           <t>Yann Sommer</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Orlando Gill</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -14073,6 +14083,11 @@
           <t>Luke Shaw</t>
         </is>
       </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Maarten Paes</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -14160,6 +14175,11 @@
           <t>Alessandro Deiola</t>
         </is>
       </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Trevoh Chalobah</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -14247,6 +14267,11 @@
           <t>Amir Rrahmani</t>
         </is>
       </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Manuel Akanji</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -14334,6 +14359,11 @@
           <t>Joshua Kimmich</t>
         </is>
       </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Strahinja Pavlović</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -14421,6 +14451,11 @@
           <t>Sergio Busquets</t>
         </is>
       </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Jérémy Jacquet</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -14508,6 +14543,11 @@
           <t>Seko Fofana</t>
         </is>
       </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Raphaël Guerreiro</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -14595,6 +14635,11 @@
           <t>Lee Jae-sung</t>
         </is>
       </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Ainsley Maitland-Niles</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -14682,6 +14727,11 @@
           <t>Rodrigo Garro</t>
         </is>
       </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Gonzalo Montiel</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -14769,6 +14819,11 @@
           <t>Gerard Moreno</t>
         </is>
       </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Danilo</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -14856,6 +14911,11 @@
           <t>Alessandro Del Piero</t>
         </is>
       </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>D Máximo Perrone</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -14943,6 +15003,11 @@
           <t>Lucas Perri</t>
         </is>
       </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>D Johnny Cardoso</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -15030,6 +15095,11 @@
           <t>Sebastián Cáceres</t>
         </is>
       </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Thiago Pitarch</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -15117,6 +15187,11 @@
           <t>Miguel Layún</t>
         </is>
       </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Valentín Barco</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -15204,6 +15279,11 @@
           <t>Lucas Digne</t>
         </is>
       </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>ID Bernardo Silva</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -15291,6 +15371,11 @@
           <t>Ross Barkley</t>
         </is>
       </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>II Emam Ashour</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -15378,6 +15463,11 @@
           <t>Yacine Adli</t>
         </is>
       </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>II Exequiel Zeballos</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -15465,6 +15555,11 @@
           <t>Álvaro Fidalgo</t>
         </is>
       </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Alan Patrick</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -15552,6 +15647,11 @@
           <t>Tommaso Baldanzi</t>
         </is>
       </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Ibrahim Mbaye</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -15639,6 +15739,11 @@
           <t>Olivier Giroud</t>
         </is>
       </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Moussa Diaby</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -15726,6 +15831,11 @@
           <t>Florian Thauvin</t>
         </is>
       </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Pierre-Emerick Aubameyang</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -15813,6 +15923,11 @@
           <t>Ciro Immobile</t>
         </is>
       </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Alexander Sørloth</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -15898,6 +16013,11 @@
       <c r="Q24" s="3" t="inlineStr">
         <is>
           <t>Gabriel Barbosa</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Zlatan Ibrahimović</t>
         </is>
       </c>
     </row>
@@ -15912,7 +16032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:R24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col width="23.44140625" bestFit="1" customWidth="1" style="11" min="1" max="1"/>
@@ -16021,6 +16141,11 @@
           <t>Club America</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Club Atlético River Plate</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
@@ -16108,6 +16233,11 @@
           <t>PT Yann Sommer</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>PT Orlando Gill</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
@@ -16195,6 +16325,11 @@
           <t>LI Luke Shaw</t>
         </is>
       </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>PT Maarten Paes</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
@@ -16282,6 +16417,11 @@
           <t>MC Alessandro Deiola</t>
         </is>
       </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>CT Trevoh Chalobah</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
@@ -16369,6 +16509,11 @@
           <t>CT Amir Rrahmani</t>
         </is>
       </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>CT Manuel Akanji</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -16456,6 +16601,11 @@
           <t>MCD Joshua Kimmich</t>
         </is>
       </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>CT Strahinja Pavlović</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -16543,6 +16693,11 @@
           <t>MCD Sergio Busquets</t>
         </is>
       </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>CT Jérémy Jacquet</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -16630,6 +16785,11 @@
           <t>MC Seko Fofana</t>
         </is>
       </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>LI Raphaël Guerreiro</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -16717,6 +16877,11 @@
           <t>MP Lee Jae-sung</t>
         </is>
       </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>LD Ainsley Maitland-Niles</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -16804,6 +16969,11 @@
           <t>MP Rodrigo Garro</t>
         </is>
       </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>LD Gonzalo Montiel</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -16891,6 +17061,11 @@
           <t>DC Gerard Moreno</t>
         </is>
       </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>LD Danilo</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
@@ -16978,6 +17153,11 @@
           <t>DC Alessandro Del Piero</t>
         </is>
       </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>MCD Máximo Perrone</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
@@ -17065,6 +17245,11 @@
           <t>PT Lucas Perri</t>
         </is>
       </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>MCD Johnny Cardoso</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -17152,6 +17337,11 @@
           <t>CT Sebastián Cáceres</t>
         </is>
       </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>MC Thiago Pitarch</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
@@ -17239,6 +17429,11 @@
           <t>LD Miguel Layún</t>
         </is>
       </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>MC Valentín Barco</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
@@ -17326,6 +17521,11 @@
           <t>LI Lucas Digne</t>
         </is>
       </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>ID Bernardo Silva</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -17413,6 +17613,11 @@
           <t>MC Ross Barkley</t>
         </is>
       </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>II Emam Ashour</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -17500,6 +17705,11 @@
           <t>MC Yacine Adli</t>
         </is>
       </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>II Exequiel Zeballos</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
@@ -17587,6 +17797,11 @@
           <t>MC Álvaro Fidalgo</t>
         </is>
       </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>MP Alan Patrick</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -17674,6 +17889,11 @@
           <t>MP Tommaso Baldanzi</t>
         </is>
       </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>ED Ibrahim Mbaye</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
@@ -17761,6 +17981,11 @@
           <t>DC Olivier Giroud</t>
         </is>
       </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>ED Moussa Diaby</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
@@ -17848,6 +18073,11 @@
           <t>ED Florian Thauvin</t>
         </is>
       </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>DC Pierre-Emerick Aubameyang</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -17935,6 +18165,11 @@
           <t>DC Ciro Immobile</t>
         </is>
       </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>DC Alexander Sørloth</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -18020,6 +18255,11 @@
       <c r="Q24" s="8" t="inlineStr">
         <is>
           <t>DC Gabriel Barbosa</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>DC Zlatan Ibrahimović</t>
         </is>
       </c>
     </row>
@@ -18034,7 +18274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="18.88671875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -18734,6 +18974,48 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Club Atlético River Plate</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>RVP</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Estadio Monumental</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Parraga</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>300000000</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>300000000</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Logos Equipos/riverplate.webp</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H19">
     <sortState ref="A2:H19">

--- a/LMI Base.xlsx
+++ b/LMI Base.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90E0F1A4-EAC1-4596-9C53-A887BDE6C792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C5D74E7-9B3A-444D-B249-69D49FA223AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro Liga" sheetId="1" r:id="rId1"/>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1750" uniqueCount="1213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1750" uniqueCount="1214">
   <si>
     <t>Inter de Milan</t>
   </si>
@@ -162,9 +162,6 @@
     <t>PT Timon Wellenreuther</t>
   </si>
   <si>
-    <t>PT Jan Oblak</t>
-  </si>
-  <si>
     <t>PT Alisson Becker</t>
   </si>
   <si>
@@ -282,18 +279,12 @@
     <t>CT Niklas Süle</t>
   </si>
   <si>
-    <t>CT Dayot Upamecano</t>
-  </si>
-  <si>
     <t>LD Jules Koundé</t>
   </si>
   <si>
     <t>CT William Saliba</t>
   </si>
   <si>
-    <t>DFC Alessandro Bastoni</t>
-  </si>
-  <si>
     <t>CT Jesús Orozco</t>
   </si>
   <si>
@@ -342,9 +333,6 @@
     <t>LI Matteo Ruggeri</t>
   </si>
   <si>
-    <t>CT Odilon Kossounou</t>
-  </si>
-  <si>
     <t>II Alejandro Garnacho</t>
   </si>
   <si>
@@ -399,18 +387,12 @@
     <t>LD Renzo Saravia</t>
   </si>
   <si>
-    <t>LI Jorrel Hato</t>
-  </si>
-  <si>
     <t>CT Robin Le Normand</t>
   </si>
   <si>
     <t>LI Marc Cucurella</t>
   </si>
   <si>
-    <t>LD Pedro Porro</t>
-  </si>
-  <si>
     <t>LI Salvador Reyes</t>
   </si>
   <si>
@@ -459,18 +441,12 @@
     <t>MCD Kalvin Phillips</t>
   </si>
   <si>
-    <t>MCD Eduardo Camavinga</t>
-  </si>
-  <si>
     <t>MC Joelinton</t>
   </si>
   <si>
     <t>CT Eric García</t>
   </si>
   <si>
-    <t>MCD Mario Lemina</t>
-  </si>
-  <si>
     <t>CT Rafael Márquez</t>
   </si>
   <si>
@@ -519,18 +495,12 @@
     <t>MC Granit Xhaka</t>
   </si>
   <si>
-    <t>MC Pape Matar Sarr</t>
-  </si>
-  <si>
     <t>LD Malo Gusto</t>
   </si>
   <si>
     <t>MC Enzo Fernández</t>
   </si>
   <si>
-    <t>MCD João Neves</t>
-  </si>
-  <si>
     <t>MP Noah Okafor</t>
   </si>
   <si>
@@ -579,18 +549,12 @@
     <t>MP Raheem Sterling</t>
   </si>
   <si>
-    <t>EI Eden Hazard</t>
-  </si>
-  <si>
     <t>DC Ademola Lookman</t>
   </si>
   <si>
     <t>MC Pedri</t>
   </si>
   <si>
-    <t>ED Lee Kang-in</t>
-  </si>
-  <si>
     <t>CT Toti Gomes</t>
   </si>
   <si>
@@ -639,9 +603,6 @@
     <t>EI Antonio Nusa</t>
   </si>
   <si>
-    <t>EI Jack Grealish</t>
-  </si>
-  <si>
     <t>DC Bryan Mbeumo</t>
   </si>
   <si>
@@ -699,18 +660,12 @@
     <t>ED Adama Traoré</t>
   </si>
   <si>
-    <t>DC Neymar</t>
-  </si>
-  <si>
     <t>ED Leroy Sané</t>
   </si>
   <si>
     <t>DC João Pedro</t>
   </si>
   <si>
-    <t>EI Cody Gakpo</t>
-  </si>
-  <si>
     <t>MP Jamal Musiala</t>
   </si>
   <si>
@@ -759,18 +714,12 @@
     <t>DC Rasmus Højlund</t>
   </si>
   <si>
-    <t>DC Serhou Guirassy</t>
-  </si>
-  <si>
     <t>MC Rodrigo De Paul</t>
   </si>
   <si>
     <t>DC David Villa</t>
   </si>
   <si>
-    <t>DC Randal Kolo Muani</t>
-  </si>
-  <si>
     <t>DC Marcus Thuram</t>
   </si>
   <si>
@@ -819,9 +768,6 @@
     <t>CT Giorgio Chiellini</t>
   </si>
   <si>
-    <t>MP Johan Manzambi</t>
-  </si>
-  <si>
     <t>MC Marc Bernal</t>
   </si>
   <si>
@@ -879,18 +825,12 @@
     <t>CT Ramy Bensebaïni</t>
   </si>
   <si>
-    <t>CT Evan Ndicka</t>
-  </si>
-  <si>
     <t>PT Keylor Navas</t>
   </si>
   <si>
     <t>CT Willian Pacho</t>
   </si>
   <si>
-    <t>DC Darwin Núñez</t>
-  </si>
-  <si>
     <t>ED Anthony Elanga</t>
   </si>
   <si>
@@ -939,18 +879,12 @@
     <t>II Samuel Lino</t>
   </si>
   <si>
-    <t>ED Jhon Arias</t>
-  </si>
-  <si>
     <t>ED Yan Diomande (P)</t>
   </si>
   <si>
     <t>CT Pau Cubarsí</t>
   </si>
   <si>
-    <t>ID Takefusa Kubo</t>
-  </si>
-  <si>
     <t>CT Perr Schuurs</t>
   </si>
   <si>
@@ -999,18 +933,12 @@
     <t>MP Giorgian de Arrascaeta</t>
   </si>
   <si>
-    <t>MC Lucas Paquetá</t>
-  </si>
-  <si>
     <t>MC Luka Modrić</t>
   </si>
   <si>
     <t>LD Reece James</t>
   </si>
   <si>
-    <t>DC Jhon Durán</t>
-  </si>
-  <si>
     <t>DC Artem Dovbyk</t>
   </si>
   <si>
@@ -1059,9 +987,6 @@
     <t>LD Julien Le Cardinal</t>
   </si>
   <si>
-    <t>ED Antony</t>
-  </si>
-  <si>
     <t>DC Kylian Mbappé</t>
   </si>
   <si>
@@ -1119,18 +1044,12 @@
     <t>LI Andrea Cambiaso</t>
   </si>
   <si>
-    <t>MC Senny Mayulu</t>
-  </si>
-  <si>
     <t>CT Éder Militão</t>
   </si>
   <si>
     <t>MCD Moisés Caicedo</t>
   </si>
   <si>
-    <t>DFC Murillo</t>
-  </si>
-  <si>
     <t>ID Samuel Chukwueze</t>
   </si>
   <si>
@@ -1179,18 +1098,12 @@
     <t>MP Reserva</t>
   </si>
   <si>
-    <t>MP Sebastian Szymański</t>
-  </si>
-  <si>
     <t>II Conor Gallagher</t>
   </si>
   <si>
     <t>MCD N'Golo Kanté</t>
   </si>
   <si>
-    <t>ED Ángel Di María</t>
-  </si>
-  <si>
     <t>PT Patrick Beach</t>
   </si>
   <si>
@@ -1239,18 +1152,12 @@
     <t>MCD Gökhan Gül</t>
   </si>
   <si>
-    <t>ED Ismaïla Sarr</t>
-  </si>
-  <si>
     <t>ED Donyell Malen</t>
   </si>
   <si>
     <t>MC Frenkie de Jong</t>
   </si>
   <si>
-    <t>DC Mauro Icardi</t>
-  </si>
-  <si>
     <t>EI Brian Rodríguez</t>
   </si>
   <si>
@@ -1299,18 +1206,12 @@
     <t>DC Ollie Watkins</t>
   </si>
   <si>
-    <t>LI Ferland Mendy</t>
-  </si>
-  <si>
     <t>MCD Manuel Locatelli</t>
   </si>
   <si>
     <t>MP Dani Olmo</t>
   </si>
   <si>
-    <t>EI Mykhailo Mudryk</t>
-  </si>
-  <si>
     <t>DC Martin Terrier</t>
   </si>
   <si>
@@ -1359,18 +1260,12 @@
     <t>MC Jobe Bellingham</t>
   </si>
   <si>
-    <t>MC Kodai Sano</t>
-  </si>
-  <si>
     <t>CT Rúben Dias</t>
   </si>
   <si>
     <t>MP Fermín López</t>
   </si>
   <si>
-    <t>MC Matheus Nunes</t>
-  </si>
-  <si>
     <t>LI Lewis Hall</t>
   </si>
   <si>
@@ -1419,18 +1314,12 @@
     <t>EI Yoane Wissa</t>
   </si>
   <si>
-    <t>CT Renato Veiga</t>
-  </si>
-  <si>
     <t>CT Lucas Beraldo</t>
   </si>
   <si>
     <t>DC Gonçalo Ramos</t>
   </si>
   <si>
-    <t>DC Igor Thiago</t>
-  </si>
-  <si>
     <t>II Alejandro Zendejas</t>
   </si>
   <si>
@@ -1479,18 +1368,12 @@
     <t>ED Yankuba Minteh</t>
   </si>
   <si>
-    <t>LD Nahuel Molina</t>
-  </si>
-  <si>
     <t>DC Sergio Agüero</t>
   </si>
   <si>
     <t>DC Ferran Torres</t>
   </si>
   <si>
-    <t>II Koki Anzai</t>
-  </si>
-  <si>
     <t>LD Jonathan Clauss</t>
   </si>
   <si>
@@ -3727,6 +3610,126 @@
   </si>
   <si>
     <t>MP Jack Hinshelwood</t>
+  </si>
+  <si>
+    <t>PT Gabriel Brazão</t>
+  </si>
+  <si>
+    <t>DFC Loïc Badé</t>
+  </si>
+  <si>
+    <t>DFC Fikayo Tomori</t>
+  </si>
+  <si>
+    <t>LI Ricardo Rodríguez</t>
+  </si>
+  <si>
+    <t>MCD Rolando Mandragora</t>
+  </si>
+  <si>
+    <t>MC Eduardo Camavinga</t>
+  </si>
+  <si>
+    <t>MCD Kaan Ayhan</t>
+  </si>
+  <si>
+    <t>MP Morgan Gibbs-White</t>
+  </si>
+  <si>
+    <t>DC Folarin Balogun</t>
+  </si>
+  <si>
+    <t>DC Dimitar Berbatov</t>
+  </si>
+  <si>
+    <t>LD Denis Zakaria</t>
+  </si>
+  <si>
+    <t>CT Alessandro Bastoni</t>
+  </si>
+  <si>
+    <t>MC João Neves</t>
+  </si>
+  <si>
+    <t>DFC Edmond Tapsoba</t>
+  </si>
+  <si>
+    <t>MP Lee Kang-in</t>
+  </si>
+  <si>
+    <t>DFC Dayot Upamecano</t>
+  </si>
+  <si>
+    <t>MP Nikola Vlašić</t>
+  </si>
+  <si>
+    <t>PT Jugador1</t>
+  </si>
+  <si>
+    <t>LD Jugador2</t>
+  </si>
+  <si>
+    <t>DFC Jugador3</t>
+  </si>
+  <si>
+    <t>DFC Jugador4</t>
+  </si>
+  <si>
+    <t>LI Jugador5</t>
+  </si>
+  <si>
+    <t>MCD Jugador6</t>
+  </si>
+  <si>
+    <t>MC Jugador7</t>
+  </si>
+  <si>
+    <t>MCD Jugador8</t>
+  </si>
+  <si>
+    <t>MP Jugador9</t>
+  </si>
+  <si>
+    <t>DC Jugador10</t>
+  </si>
+  <si>
+    <t>DC Jugador11</t>
+  </si>
+  <si>
+    <t>LD Jugador12</t>
+  </si>
+  <si>
+    <t>CT Jugador13</t>
+  </si>
+  <si>
+    <t>MC Jugador14</t>
+  </si>
+  <si>
+    <t>PT Jugador15</t>
+  </si>
+  <si>
+    <t>DFC Jugador16</t>
+  </si>
+  <si>
+    <t>MP Jugador17</t>
+  </si>
+  <si>
+    <t>MP Jugador18</t>
+  </si>
+  <si>
+    <t>LI Jugador21</t>
+  </si>
+  <si>
+    <t>DFC Jugador22</t>
+  </si>
+  <si>
+    <t>MP Jugador23</t>
+  </si>
+  <si>
+    <t>DFC Jugador19</t>
+  </si>
+  <si>
+    <t>MP Jugador20</t>
   </si>
 </sst>
 </file>
@@ -4176,16 +4179,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>479</v>
+        <v>440</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>480</v>
+        <v>441</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>481</v>
+        <v>442</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>482</v>
+        <v>443</v>
       </c>
     </row>
   </sheetData>
@@ -4215,33 +4218,33 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>480</v>
+        <v>441</v>
       </c>
       <c r="B1" t="s">
-        <v>484</v>
+        <v>445</v>
       </c>
       <c r="C1" t="s">
-        <v>1095</v>
+        <v>1056</v>
       </c>
       <c r="D1" t="s">
-        <v>1096</v>
+        <v>1057</v>
       </c>
       <c r="E1" t="s">
-        <v>1097</v>
+        <v>1058</v>
       </c>
       <c r="F1" t="s">
-        <v>1098</v>
+        <v>1059</v>
       </c>
       <c r="G1" t="s">
-        <v>1099</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>1100</v>
+        <v>1061</v>
       </c>
       <c r="B6" t="s">
-        <v>1101</v>
+        <v>1062</v>
       </c>
       <c r="C6" t="s">
         <v>12</v>
@@ -4256,15 +4259,15 @@
         <v>2</v>
       </c>
       <c r="G6" t="s">
-        <v>1102</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>537</v>
+        <v>498</v>
       </c>
       <c r="B7" t="s">
-        <v>1101</v>
+        <v>1062</v>
       </c>
       <c r="C7" t="s">
         <v>12</v>
@@ -4279,15 +4282,15 @@
         <v>2</v>
       </c>
       <c r="G7" t="s">
-        <v>1102</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>1103</v>
+        <v>1064</v>
       </c>
       <c r="B8" t="s">
-        <v>1101</v>
+        <v>1062</v>
       </c>
       <c r="C8" t="s">
         <v>13</v>
@@ -4302,15 +4305,15 @@
         <v>2</v>
       </c>
       <c r="G8" t="s">
-        <v>1104</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>1105</v>
+        <v>1066</v>
       </c>
       <c r="B9" t="s">
-        <v>1101</v>
+        <v>1062</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -4325,15 +4328,15 @@
         <v>2</v>
       </c>
       <c r="G9" t="s">
-        <v>1104</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>1106</v>
+        <v>1067</v>
       </c>
       <c r="B10" t="s">
-        <v>1101</v>
+        <v>1062</v>
       </c>
       <c r="C10" t="s">
         <v>0</v>
@@ -4348,18 +4351,18 @@
         <v>2</v>
       </c>
       <c r="G10" t="s">
-        <v>1104</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>1107</v>
+        <v>1068</v>
       </c>
       <c r="B11" t="s">
-        <v>1101</v>
+        <v>1062</v>
       </c>
       <c r="C11" t="s">
-        <v>1108</v>
+        <v>1069</v>
       </c>
       <c r="D11" t="s">
         <v>13</v>
@@ -4371,21 +4374,21 @@
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>1104</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>1109</v>
+        <v>1070</v>
       </c>
       <c r="B12" t="s">
-        <v>1101</v>
+        <v>1062</v>
       </c>
       <c r="C12" t="s">
         <v>10</v>
       </c>
       <c r="D12" t="s">
-        <v>1108</v>
+        <v>1069</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -4394,18 +4397,18 @@
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>1104</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>1110</v>
+        <v>1071</v>
       </c>
       <c r="B13" t="s">
-        <v>1101</v>
+        <v>1062</v>
       </c>
       <c r="C13" t="s">
-        <v>1108</v>
+        <v>1069</v>
       </c>
       <c r="D13" t="s">
         <v>10</v>
@@ -4417,7 +4420,7 @@
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>1104</v>
+        <v>1065</v>
       </c>
     </row>
   </sheetData>
@@ -4433,21 +4436,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>1111</v>
+        <v>1072</v>
       </c>
       <c r="B1" t="s">
-        <v>1112</v>
+        <v>1073</v>
       </c>
       <c r="C1" t="s">
-        <v>1113</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1114</v>
+        <v>1075</v>
       </c>
       <c r="B2" t="s">
-        <v>1010</v>
+        <v>971</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -4455,10 +4458,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1114</v>
+        <v>1075</v>
       </c>
       <c r="B3" t="s">
-        <v>1115</v>
+        <v>1076</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -4466,10 +4469,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>1114</v>
+        <v>1075</v>
       </c>
       <c r="B4" t="s">
-        <v>1116</v>
+        <v>1077</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -4477,10 +4480,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>1114</v>
+        <v>1075</v>
       </c>
       <c r="B5" t="s">
-        <v>1117</v>
+        <v>1078</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -4488,10 +4491,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>1114</v>
+        <v>1075</v>
       </c>
       <c r="B6" t="s">
-        <v>996</v>
+        <v>957</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -4499,10 +4502,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>1118</v>
+        <v>1079</v>
       </c>
       <c r="B7" t="s">
-        <v>1119</v>
+        <v>1080</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -4510,10 +4513,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>1118</v>
+        <v>1079</v>
       </c>
       <c r="B8" t="s">
-        <v>1120</v>
+        <v>1081</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -4521,10 +4524,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>1118</v>
+        <v>1079</v>
       </c>
       <c r="B9" t="s">
-        <v>996</v>
+        <v>957</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -4532,10 +4535,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>1118</v>
+        <v>1079</v>
       </c>
       <c r="B10" t="s">
-        <v>1010</v>
+        <v>971</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -4543,10 +4546,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>1118</v>
+        <v>1079</v>
       </c>
       <c r="B11" t="s">
-        <v>1025</v>
+        <v>986</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -4554,10 +4557,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>1121</v>
+        <v>1082</v>
       </c>
       <c r="B12" t="s">
-        <v>1117</v>
+        <v>1078</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -4565,10 +4568,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>1121</v>
+        <v>1082</v>
       </c>
       <c r="B13" t="s">
-        <v>996</v>
+        <v>957</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -4576,10 +4579,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>1121</v>
+        <v>1082</v>
       </c>
       <c r="B14" t="s">
-        <v>1025</v>
+        <v>986</v>
       </c>
       <c r="C14">
         <v>2</v>
@@ -4617,1274 +4620,1274 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>483</v>
+        <v>444</v>
       </c>
       <c r="B1" t="s">
-        <v>487</v>
+        <v>448</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>491</v>
+        <v>452</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>492</v>
+        <v>453</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>486</v>
+        <v>447</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>493</v>
+        <v>454</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>495</v>
+        <v>456</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>497</v>
+        <v>458</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>499</v>
+        <v>460</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>500</v>
+        <v>461</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>494</v>
+        <v>455</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>11</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>501</v>
+        <v>462</v>
       </c>
       <c r="O1" s="3" t="s">
         <v>17</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>502</v>
+        <v>463</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>503</v>
+        <v>464</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>530</v>
+        <v>491</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>888</v>
+        <v>849</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>1122</v>
+        <v>1083</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>533</v>
+        <v>494</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>534</v>
+        <v>495</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>535</v>
+        <v>496</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>1123</v>
+        <v>1084</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>537</v>
+        <v>498</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>538</v>
+        <v>499</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>1124</v>
+        <v>1085</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>540</v>
+        <v>501</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>541</v>
+        <v>502</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>1125</v>
+        <v>1086</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>543</v>
+        <v>504</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>544</v>
+        <v>505</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>545</v>
+        <v>506</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>546</v>
+        <v>507</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>550</v>
+        <v>511</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>1126</v>
+        <v>1087</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>1127</v>
+        <v>1088</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>553</v>
+        <v>514</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>554</v>
+        <v>515</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>555</v>
+        <v>516</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>576</v>
+        <v>537</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>557</v>
+        <v>518</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>558</v>
+        <v>519</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>561</v>
+        <v>522</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>560</v>
+        <v>521</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>1128</v>
+        <v>1089</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>562</v>
+        <v>523</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>563</v>
+        <v>524</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>564</v>
+        <v>525</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>1129</v>
+        <v>1090</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>566</v>
+        <v>527</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>570</v>
+        <v>531</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>1130</v>
+        <v>1091</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>1131</v>
+        <v>1092</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>1132</v>
+        <v>1093</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>574</v>
+        <v>535</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>575</v>
+        <v>536</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>1133</v>
+        <v>1094</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>577</v>
+        <v>538</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>578</v>
+        <v>539</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>579</v>
+        <v>540</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>580</v>
+        <v>541</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>581</v>
+        <v>542</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>582</v>
+        <v>543</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>583</v>
+        <v>544</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>584</v>
+        <v>545</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>585</v>
+        <v>546</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>586</v>
+        <v>547</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>590</v>
+        <v>551</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>611</v>
+        <v>572</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>612</v>
+        <v>573</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>593</v>
+        <v>554</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>594</v>
+        <v>555</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>1134</v>
+        <v>1095</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>636</v>
+        <v>597</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>597</v>
+        <v>558</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>598</v>
+        <v>559</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>696</v>
+        <v>657</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>600</v>
+        <v>561</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>601</v>
+        <v>562</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>1135</v>
+        <v>1096</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>603</v>
+        <v>564</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>604</v>
+        <v>565</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>605</v>
+        <v>566</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>606</v>
+        <v>567</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>610</v>
+        <v>571</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>1136</v>
+        <v>1097</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>1137</v>
+        <v>1098</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>613</v>
+        <v>574</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>614</v>
+        <v>575</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>615</v>
+        <v>576</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>715</v>
+        <v>676</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>617</v>
+        <v>578</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>618</v>
+        <v>579</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>619</v>
+        <v>580</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>620</v>
+        <v>581</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>621</v>
+        <v>582</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>622</v>
+        <v>583</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>1138</v>
+        <v>1099</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>624</v>
+        <v>585</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>625</v>
+        <v>586</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>626</v>
+        <v>587</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>630</v>
+        <v>591</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>571</v>
+        <v>532</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>909</v>
+        <v>870</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>633</v>
+        <v>594</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>634</v>
+        <v>595</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>635</v>
+        <v>596</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>734</v>
+        <v>695</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>637</v>
+        <v>598</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>638</v>
+        <v>599</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>639</v>
+        <v>600</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>640</v>
+        <v>601</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>641</v>
+        <v>602</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>1139</v>
+        <v>1100</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>643</v>
+        <v>604</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>644</v>
+        <v>605</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>645</v>
+        <v>606</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>646</v>
+        <v>607</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>650</v>
+        <v>611</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>828</v>
+        <v>789</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>1140</v>
+        <v>1101</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>653</v>
+        <v>614</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>654</v>
+        <v>615</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>655</v>
+        <v>616</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>814</v>
+        <v>775</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>657</v>
+        <v>618</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>658</v>
+        <v>619</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>659</v>
+        <v>620</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>1141</v>
+        <v>1102</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>661</v>
+        <v>622</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>662</v>
+        <v>623</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>860</v>
+        <v>821</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>664</v>
+        <v>625</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>665</v>
+        <v>626</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>666</v>
+        <v>627</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>670</v>
+        <v>631</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>1142</v>
+        <v>1103</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>1143</v>
+        <v>1104</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>673</v>
+        <v>634</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>674</v>
+        <v>635</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>1144</v>
+        <v>1105</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>853</v>
+        <v>814</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>677</v>
+        <v>638</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>678</v>
+        <v>639</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>1145</v>
+        <v>1106</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>1146</v>
+        <v>1107</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>681</v>
+        <v>642</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>899</v>
+        <v>860</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>683</v>
+        <v>644</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>684</v>
+        <v>645</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>685</v>
+        <v>646</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>686</v>
+        <v>647</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>1147</v>
+        <v>1108</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>671</v>
+        <v>632</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>1148</v>
+        <v>1109</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>693</v>
+        <v>654</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>694</v>
+        <v>655</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>695</v>
+        <v>656</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>913</v>
+        <v>874</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>697</v>
+        <v>658</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>698</v>
+        <v>659</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>699</v>
+        <v>660</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>937</v>
+        <v>898</v>
       </c>
       <c r="L10" s="3" t="s">
+        <v>1071</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="N10" s="3" t="s">
         <v>1110</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>702</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>1149</v>
-      </c>
       <c r="O10" s="3" t="s">
-        <v>704</v>
+        <v>665</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>705</v>
+        <v>666</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>706</v>
+        <v>667</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>709</v>
+        <v>670</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>1150</v>
+        <v>1111</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>1151</v>
+        <v>1112</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>730</v>
+        <v>691</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>713</v>
+        <v>674</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>714</v>
+        <v>675</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>893</v>
+        <v>854</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>716</v>
+        <v>677</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>717</v>
+        <v>678</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>718</v>
+        <v>679</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>825</v>
+        <v>786</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>720</v>
+        <v>681</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>721</v>
+        <v>682</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>722</v>
+        <v>683</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>723</v>
+        <v>684</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>724</v>
+        <v>685</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>725</v>
+        <v>686</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>1152</v>
+        <v>1113</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>1153</v>
+        <v>1114</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>1154</v>
+        <v>1115</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>731</v>
+        <v>692</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>732</v>
+        <v>693</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>1155</v>
+        <v>1116</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>1156</v>
+        <v>1117</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>735</v>
+        <v>696</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>736</v>
+        <v>697</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>811</v>
+        <v>772</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>738</v>
+        <v>699</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>739</v>
+        <v>700</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>740</v>
+        <v>701</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>741</v>
+        <v>702</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>742</v>
+        <v>703</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>743</v>
+        <v>704</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>744</v>
+        <v>705</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>1157</v>
+        <v>1118</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>868</v>
+        <v>829</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>729</v>
+        <v>690</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>751</v>
+        <v>712</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>752</v>
+        <v>713</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>753</v>
+        <v>714</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>1158</v>
+        <v>1119</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>755</v>
+        <v>716</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>756</v>
+        <v>717</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>1159</v>
+        <v>1120</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>1160</v>
+        <v>1121</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>548</v>
+        <v>509</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>758</v>
+        <v>719</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>761</v>
+        <v>722</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>1161</v>
+        <v>1122</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>763</v>
+        <v>724</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>764</v>
+        <v>725</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>1162</v>
+        <v>1123</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>749</v>
+        <v>710</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>1163</v>
+        <v>1124</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>771</v>
+        <v>732</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>772</v>
+        <v>733</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>1164</v>
+        <v>1125</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>1165</v>
+        <v>1126</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>775</v>
+        <v>736</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>776</v>
+        <v>737</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>777</v>
+        <v>738</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>778</v>
+        <v>739</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>779</v>
+        <v>740</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>607</v>
+        <v>568</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>1166</v>
+        <v>1127</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>782</v>
+        <v>743</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>783</v>
+        <v>744</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>784</v>
+        <v>745</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>1167</v>
+        <v>1128</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>691</v>
+        <v>652</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>1168</v>
+        <v>1129</v>
       </c>
       <c r="D15" s="5" t="s">
+        <v>715</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>753</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>754</v>
       </c>
-      <c r="E15" s="5" t="s">
-        <v>792</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>793</v>
-      </c>
       <c r="G15" s="3" t="s">
-        <v>656</v>
+        <v>617</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>795</v>
+        <v>756</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>796</v>
+        <v>757</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>797</v>
+        <v>758</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>798</v>
+        <v>759</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>799</v>
+        <v>760</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>800</v>
+        <v>761</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>1169</v>
+        <v>1130</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>802</v>
+        <v>763</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>1170</v>
+        <v>1131</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>804</v>
+        <v>765</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>808</v>
+        <v>769</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>769</v>
+        <v>730</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>1171</v>
+        <v>1132</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>737</v>
+        <v>698</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>812</v>
+        <v>773</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>813</v>
+        <v>774</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>1172</v>
+        <v>1133</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>815</v>
+        <v>776</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>816</v>
+        <v>777</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>817</v>
+        <v>778</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>902</v>
+        <v>863</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>1107</v>
+        <v>1068</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>820</v>
+        <v>781</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>801</v>
+        <v>762</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>1173</v>
+        <v>1134</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>1174</v>
+        <v>1135</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>824</v>
+        <v>785</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>827</v>
+        <v>788</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>809</v>
+        <v>770</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>1175</v>
+        <v>1136</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>830</v>
+        <v>791</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>831</v>
+        <v>792</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>1176</v>
+        <v>1137</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>774</v>
+        <v>735</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>834</v>
+        <v>795</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>835</v>
+        <v>796</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>836</v>
+        <v>797</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>1177</v>
+        <v>1138</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>819</v>
+        <v>780</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>839</v>
+        <v>800</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>821</v>
+        <v>782</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>841</v>
+        <v>802</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>842</v>
+        <v>803</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>843</v>
+        <v>804</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>847</v>
+        <v>808</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>1178</v>
+        <v>1139</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>1179</v>
+        <v>1140</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>850</v>
+        <v>811</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>851</v>
+        <v>812</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>852</v>
+        <v>813</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>1180</v>
+        <v>1141</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>854</v>
+        <v>815</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>855</v>
+        <v>816</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>856</v>
+        <v>817</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>837</v>
+        <v>798</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>838</v>
+        <v>799</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>859</v>
+        <v>820</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>840</v>
+        <v>801</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>861</v>
+        <v>822</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>1181</v>
+        <v>1142</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>863</v>
+        <v>824</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>932</v>
+        <v>893</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>1182</v>
+        <v>1143</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>1183</v>
+        <v>1144</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>870</v>
+        <v>831</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>871</v>
+        <v>832</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>872</v>
+        <v>833</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>1184</v>
+        <v>1145</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>874</v>
+        <v>835</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>875</v>
+        <v>836</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>1185</v>
+        <v>1146</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>1186</v>
+        <v>1147</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>878</v>
+        <v>839</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>879</v>
+        <v>840</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>880</v>
+        <v>841</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>1187</v>
+        <v>1148</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>1188</v>
+        <v>1149</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>883</v>
+        <v>844</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>632</v>
+        <v>593</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>1189</v>
+        <v>1150</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>1190</v>
+        <v>1151</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>890</v>
+        <v>851</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>891</v>
+        <v>852</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>892</v>
+        <v>853</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>933</v>
+        <v>894</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>894</v>
+        <v>855</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>895</v>
+        <v>856</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>896</v>
+        <v>857</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>1191</v>
+        <v>1152</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>898</v>
+        <v>859</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>962</v>
+        <v>923</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>920</v>
+        <v>881</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>901</v>
+        <v>862</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>1192</v>
+        <v>1153</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>903</v>
+        <v>864</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>907</v>
+        <v>868</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>1193</v>
+        <v>1154</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>1194</v>
+        <v>1155</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>910</v>
+        <v>871</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>911</v>
+        <v>872</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>912</v>
+        <v>873</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>1195</v>
+        <v>1156</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>914</v>
+        <v>875</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>915</v>
+        <v>876</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>1196</v>
+        <v>1157</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>917</v>
+        <v>878</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>1197</v>
+        <v>1158</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>1198</v>
+        <v>1159</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>940</v>
+        <v>901</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>1199</v>
+        <v>1160</v>
       </c>
       <c r="P21" s="3" t="s">
-        <v>922</v>
+        <v>883</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>923</v>
+        <v>884</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>927</v>
+        <v>888</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>948</v>
+        <v>909</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>1200</v>
+        <v>1161</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>1201</v>
+        <v>1162</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>931</v>
+        <v>892</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>1202</v>
+        <v>1163</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>791</v>
+        <v>752</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>1203</v>
+        <v>1164</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>935</v>
+        <v>896</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>936</v>
+        <v>897</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>1204</v>
+        <v>1165</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>938</v>
+        <v>899</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>939</v>
+        <v>900</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>900</v>
+        <v>861</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>941</v>
+        <v>902</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>942</v>
+        <v>903</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>943</v>
+        <v>904</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>1205</v>
+        <v>1166</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>968</v>
+        <v>929</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>928</v>
+        <v>889</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>950</v>
+        <v>911</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>951</v>
+        <v>912</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>952</v>
+        <v>913</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>833</v>
+        <v>794</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>954</v>
+        <v>915</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>955</v>
+        <v>916</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>1206</v>
+        <v>1167</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>957</v>
+        <v>918</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>958</v>
+        <v>919</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>1207</v>
+        <v>1168</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>960</v>
+        <v>921</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>961</v>
+        <v>922</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>1208</v>
+        <v>1169</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>963</v>
+        <v>924</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>967</v>
+        <v>928</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>1209</v>
+        <v>1170</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>1210</v>
+        <v>1171</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>970</v>
+        <v>931</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>971</v>
+        <v>932</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>972</v>
+        <v>933</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>953</v>
+        <v>914</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>974</v>
+        <v>935</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>975</v>
+        <v>936</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>976</v>
+        <v>937</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>977</v>
+        <v>938</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>978</v>
+        <v>939</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>979</v>
+        <v>940</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>710</v>
+        <v>671</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>981</v>
+        <v>942</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>1211</v>
+        <v>1172</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>983</v>
+        <v>944</v>
       </c>
     </row>
   </sheetData>
@@ -5908,46 +5911,46 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>483</v>
+        <v>444</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>483</v>
+        <v>444</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>484</v>
+        <v>445</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>485</v>
+        <v>446</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>486</v>
+        <v>447</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>484</v>
+        <v>445</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>485</v>
+        <v>446</v>
       </c>
       <c r="K1" s="5"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>487</v>
+        <v>448</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>488</v>
+        <v>449</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>489</v>
+        <v>450</v>
       </c>
       <c r="E2" s="3">
         <v>103</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>490</v>
+        <v>451</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>489</v>
+        <v>450</v>
       </c>
       <c r="I2" s="6">
         <v>101</v>
@@ -5955,50 +5958,50 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>491</v>
+        <v>452</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>492</v>
+        <v>453</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>491</v>
+        <v>452</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>484</v>
+        <v>445</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>485</v>
+        <v>446</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>484</v>
+        <v>445</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>485</v>
+        <v>446</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>486</v>
+        <v>447</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>489</v>
+        <v>450</v>
       </c>
       <c r="E5" s="6">
         <v>107</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>489</v>
+        <v>450</v>
       </c>
       <c r="I5" s="6">
         <v>101</v>
@@ -6011,45 +6014,45 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>493</v>
+        <v>454</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>484</v>
+        <v>445</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>485</v>
+        <v>446</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>494</v>
+        <v>455</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>484</v>
+        <v>445</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>485</v>
+        <v>446</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>495</v>
+        <v>456</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>489</v>
+        <v>450</v>
       </c>
       <c r="E8" s="6">
         <v>102</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>237</v>
+        <v>220</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>496</v>
+        <v>457</v>
       </c>
       <c r="I8" s="6">
         <v>106</v>
@@ -6057,13 +6060,13 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>497</v>
+        <v>458</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>498</v>
+        <v>459</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>489</v>
+        <v>450</v>
       </c>
       <c r="I9" s="6">
         <v>103</v>
@@ -6071,22 +6074,22 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>499</v>
+        <v>460</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>484</v>
+        <v>445</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>485</v>
+        <v>446</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>496</v>
+        <v>457</v>
       </c>
       <c r="I10" s="6">
         <v>102</v>
@@ -6094,13 +6097,13 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>500</v>
+        <v>461</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>489</v>
+        <v>450</v>
       </c>
       <c r="E11" s="6">
         <v>104</v>
@@ -6108,16 +6111,16 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>494</v>
+        <v>455</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>495</v>
+        <v>456</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>484</v>
+        <v>445</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>485</v>
+        <v>446</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -6125,19 +6128,19 @@
         <v>11</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>500</v>
+        <v>461</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>484</v>
+        <v>445</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>485</v>
+        <v>446</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>471</v>
+        <v>432</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>489</v>
+        <v>450</v>
       </c>
       <c r="I13" s="6">
         <v>107</v>
@@ -6145,13 +6148,13 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>501</v>
+        <v>462</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>489</v>
+        <v>450</v>
       </c>
       <c r="E14" s="6">
         <v>106</v>
@@ -6162,33 +6165,33 @@
         <v>17</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>496</v>
+        <v>457</v>
       </c>
       <c r="E15" s="6">
         <v>105</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>502</v>
+        <v>463</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>484</v>
+        <v>445</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>485</v>
+        <v>446</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>502</v>
+        <v>463</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>489</v>
+        <v>450</v>
       </c>
       <c r="I16" s="6">
         <v>105</v>
@@ -6196,53 +6199,53 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>503</v>
+        <v>464</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>493</v>
+        <v>454</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>484</v>
+        <v>445</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>485</v>
+        <v>446</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C18" s="8" t="s">
-        <v>504</v>
+        <v>465</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>489</v>
+        <v>450</v>
       </c>
       <c r="E18" s="6">
         <v>103</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>492</v>
+        <v>453</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>484</v>
+        <v>445</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>485</v>
+        <v>446</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C19" s="8" t="s">
-        <v>505</v>
+        <v>466</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>496</v>
+        <v>457</v>
       </c>
       <c r="E19" s="6">
         <v>105</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>464</v>
+        <v>426</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>489</v>
+        <v>450</v>
       </c>
       <c r="I19">
         <v>104</v>
@@ -6250,21 +6253,21 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C21" s="3" t="s">
-        <v>503</v>
+        <v>464</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>484</v>
+        <v>445</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>485</v>
+        <v>446</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C22" s="8" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="D22" t="s">
-        <v>489</v>
+        <v>450</v>
       </c>
       <c r="E22">
         <v>101</v>
@@ -6286,27 +6289,27 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>506</v>
+        <v>467</v>
       </c>
       <c r="B1" t="s">
-        <v>507</v>
+        <v>468</v>
       </c>
       <c r="C1" t="s">
-        <v>508</v>
+        <v>469</v>
       </c>
       <c r="D1" t="s">
-        <v>509</v>
+        <v>470</v>
       </c>
       <c r="E1" t="s">
-        <v>510</v>
+        <v>471</v>
       </c>
       <c r="F1" t="s">
-        <v>511</v>
+        <v>472</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>512</v>
+        <v>473</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
@@ -6315,21 +6318,21 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>513</v>
+        <v>474</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>514</v>
+        <v>475</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>515</v>
+        <v>476</v>
       </c>
       <c r="B3" t="s">
-        <v>516</v>
+        <v>477</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -6341,15 +6344,15 @@
         <v>3</v>
       </c>
       <c r="F3" t="s">
-        <v>514</v>
+        <v>475</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>517</v>
+        <v>478</v>
       </c>
       <c r="B4" t="s">
-        <v>518</v>
+        <v>479</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -6361,12 +6364,12 @@
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>514</v>
+        <v>475</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>519</v>
+        <v>480</v>
       </c>
       <c r="B5" t="s">
         <v>0</v>
@@ -6381,12 +6384,12 @@
         <v>3</v>
       </c>
       <c r="F5" t="s">
-        <v>514</v>
+        <v>475</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>520</v>
+        <v>481</v>
       </c>
       <c r="B6" t="s">
         <v>10</v>
@@ -6401,12 +6404,12 @@
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>514</v>
+        <v>475</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>521</v>
+        <v>482</v>
       </c>
       <c r="B7" t="s">
         <v>11</v>
@@ -6421,12 +6424,12 @@
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>514</v>
+        <v>475</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>522</v>
+        <v>483</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -6441,7 +6444,7 @@
         <v>4</v>
       </c>
       <c r="F8" t="s">
-        <v>514</v>
+        <v>475</v>
       </c>
     </row>
   </sheetData>
@@ -6460,27 +6463,27 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>506</v>
+        <v>467</v>
       </c>
       <c r="B1" t="s">
-        <v>507</v>
+        <v>468</v>
       </c>
       <c r="C1" t="s">
-        <v>508</v>
+        <v>469</v>
       </c>
       <c r="D1" t="s">
-        <v>509</v>
+        <v>470</v>
       </c>
       <c r="E1" t="s">
-        <v>510</v>
+        <v>471</v>
       </c>
       <c r="F1" t="s">
-        <v>511</v>
+        <v>472</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>512</v>
+        <v>473</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -6489,38 +6492,38 @@
         <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>523</v>
+        <v>484</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>514</v>
+        <v>475</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>515</v>
+        <v>476</v>
       </c>
       <c r="B3" t="s">
-        <v>524</v>
+        <v>485</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>518</v>
+        <v>479</v>
       </c>
       <c r="E3">
         <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>514</v>
+        <v>475</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>517</v>
+        <v>478</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
@@ -6535,12 +6538,12 @@
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>514</v>
+        <v>475</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>519</v>
+        <v>480</v>
       </c>
       <c r="B5" t="s">
         <v>11</v>
@@ -6555,32 +6558,32 @@
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>514</v>
+        <v>475</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>520</v>
+        <v>481</v>
       </c>
       <c r="B6" t="s">
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>525</v>
+        <v>486</v>
       </c>
       <c r="D6" t="s">
-        <v>518</v>
+        <v>479</v>
       </c>
       <c r="E6" t="s">
-        <v>526</v>
+        <v>487</v>
       </c>
       <c r="F6" t="s">
-        <v>514</v>
+        <v>475</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>521</v>
+        <v>482</v>
       </c>
       <c r="B7" t="s">
         <v>6</v>
@@ -6595,12 +6598,12 @@
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>514</v>
+        <v>475</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>522</v>
+        <v>483</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
@@ -6615,7 +6618,7 @@
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>514</v>
+        <v>475</v>
       </c>
     </row>
   </sheetData>
@@ -6636,16 +6639,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>479</v>
+        <v>440</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>480</v>
+        <v>441</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>481</v>
+        <v>442</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>482</v>
+        <v>443</v>
       </c>
     </row>
   </sheetData>
@@ -6671,16 +6674,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>479</v>
+        <v>440</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>480</v>
+        <v>441</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>481</v>
+        <v>442</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>482</v>
+        <v>443</v>
       </c>
     </row>
   </sheetData>
@@ -6720,1490 +6723,1490 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>483</v>
+        <v>444</v>
       </c>
       <c r="B1" t="s">
-        <v>487</v>
+        <v>448</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>491</v>
+        <v>452</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>492</v>
+        <v>453</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>486</v>
+        <v>447</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>493</v>
+        <v>454</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>495</v>
+        <v>456</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>497</v>
+        <v>458</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>499</v>
+        <v>460</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>500</v>
+        <v>461</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>494</v>
+        <v>455</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>11</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>501</v>
+        <v>462</v>
       </c>
       <c r="O1" s="3" t="s">
         <v>17</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>502</v>
+        <v>463</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>503</v>
+        <v>464</v>
       </c>
       <c r="R1" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
       <c r="S1" t="s">
-        <v>528</v>
+        <v>489</v>
       </c>
       <c r="T1" t="s">
-        <v>529</v>
+        <v>490</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>530</v>
+        <v>491</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>531</v>
+        <v>492</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>532</v>
+        <v>493</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>533</v>
+        <v>494</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>534</v>
+        <v>495</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>535</v>
+        <v>496</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>536</v>
+        <v>497</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>537</v>
+        <v>498</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>538</v>
+        <v>499</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>539</v>
+        <v>500</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>540</v>
+        <v>501</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>541</v>
+        <v>502</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>542</v>
+        <v>503</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>543</v>
+        <v>504</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>544</v>
+        <v>505</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>545</v>
+        <v>506</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>546</v>
+        <v>507</v>
       </c>
       <c r="R2" t="s">
-        <v>547</v>
+        <v>508</v>
       </c>
       <c r="S2" t="s">
-        <v>548</v>
+        <v>509</v>
       </c>
       <c r="T2" t="s">
-        <v>549</v>
+        <v>510</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>550</v>
+        <v>511</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>551</v>
+        <v>512</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>552</v>
+        <v>513</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>553</v>
+        <v>514</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>554</v>
+        <v>515</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>555</v>
+        <v>516</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>556</v>
+        <v>517</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>557</v>
+        <v>518</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>558</v>
+        <v>519</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>559</v>
+        <v>520</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>560</v>
+        <v>521</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>561</v>
+        <v>522</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>562</v>
+        <v>523</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>563</v>
+        <v>524</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>564</v>
+        <v>525</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>565</v>
+        <v>526</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>566</v>
+        <v>527</v>
       </c>
       <c r="R3" t="s">
-        <v>567</v>
+        <v>528</v>
       </c>
       <c r="S3" t="s">
-        <v>568</v>
+        <v>529</v>
       </c>
       <c r="T3" t="s">
-        <v>569</v>
+        <v>530</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>570</v>
+        <v>531</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>571</v>
+        <v>532</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>572</v>
+        <v>533</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>573</v>
+        <v>534</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>574</v>
+        <v>535</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>575</v>
+        <v>536</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>576</v>
+        <v>537</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>577</v>
+        <v>538</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>578</v>
+        <v>539</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>579</v>
+        <v>540</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>580</v>
+        <v>541</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>581</v>
+        <v>542</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>582</v>
+        <v>543</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>583</v>
+        <v>544</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>584</v>
+        <v>545</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>585</v>
+        <v>546</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>586</v>
+        <v>547</v>
       </c>
       <c r="R4" t="s">
-        <v>587</v>
+        <v>548</v>
       </c>
       <c r="S4" t="s">
-        <v>588</v>
+        <v>549</v>
       </c>
       <c r="T4" t="s">
-        <v>589</v>
+        <v>550</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>590</v>
+        <v>551</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>591</v>
+        <v>552</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>592</v>
+        <v>553</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>593</v>
+        <v>554</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>594</v>
+        <v>555</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>595</v>
+        <v>556</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>596</v>
+        <v>557</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>597</v>
+        <v>558</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>598</v>
+        <v>559</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>599</v>
+        <v>560</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>600</v>
+        <v>561</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>601</v>
+        <v>562</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>602</v>
+        <v>563</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>603</v>
+        <v>564</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>604</v>
+        <v>565</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>605</v>
+        <v>566</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>606</v>
+        <v>567</v>
       </c>
       <c r="R5" t="s">
-        <v>607</v>
+        <v>568</v>
       </c>
       <c r="S5" t="s">
-        <v>608</v>
+        <v>569</v>
       </c>
       <c r="T5" t="s">
-        <v>609</v>
+        <v>570</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>610</v>
+        <v>571</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>611</v>
+        <v>572</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>612</v>
+        <v>573</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>613</v>
+        <v>574</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>614</v>
+        <v>575</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>615</v>
+        <v>576</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>616</v>
+        <v>577</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>617</v>
+        <v>578</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>618</v>
+        <v>579</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>619</v>
+        <v>580</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>620</v>
+        <v>581</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>621</v>
+        <v>582</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>622</v>
+        <v>583</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>623</v>
+        <v>584</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>624</v>
+        <v>585</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>625</v>
+        <v>586</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>626</v>
+        <v>587</v>
       </c>
       <c r="R6" t="s">
-        <v>627</v>
+        <v>588</v>
       </c>
       <c r="S6" t="s">
-        <v>628</v>
+        <v>589</v>
       </c>
       <c r="T6" t="s">
-        <v>629</v>
+        <v>590</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>630</v>
+        <v>591</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>631</v>
+        <v>592</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>632</v>
+        <v>593</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>633</v>
+        <v>594</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>634</v>
+        <v>595</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>635</v>
+        <v>596</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>636</v>
+        <v>597</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>637</v>
+        <v>598</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>638</v>
+        <v>599</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>639</v>
+        <v>600</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>640</v>
+        <v>601</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>641</v>
+        <v>602</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>642</v>
+        <v>603</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>643</v>
+        <v>604</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>644</v>
+        <v>605</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>645</v>
+        <v>606</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="R7" t="s">
-        <v>647</v>
+        <v>608</v>
       </c>
       <c r="S7" t="s">
-        <v>648</v>
+        <v>609</v>
       </c>
       <c r="T7" t="s">
-        <v>649</v>
+        <v>610</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>650</v>
+        <v>611</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>651</v>
+        <v>612</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>652</v>
+        <v>613</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>653</v>
+        <v>614</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>654</v>
+        <v>615</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>655</v>
+        <v>616</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>656</v>
+        <v>617</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>657</v>
+        <v>618</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>658</v>
+        <v>619</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>659</v>
+        <v>620</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>660</v>
+        <v>621</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>661</v>
+        <v>622</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>662</v>
+        <v>623</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>663</v>
+        <v>624</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>664</v>
+        <v>625</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>665</v>
+        <v>626</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>666</v>
+        <v>627</v>
       </c>
       <c r="R8" t="s">
-        <v>667</v>
+        <v>628</v>
       </c>
       <c r="S8" t="s">
-        <v>668</v>
+        <v>629</v>
       </c>
       <c r="T8" t="s">
-        <v>669</v>
+        <v>630</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>670</v>
+        <v>631</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>671</v>
+        <v>632</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>672</v>
+        <v>633</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>673</v>
+        <v>634</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>674</v>
+        <v>635</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>675</v>
+        <v>636</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>676</v>
+        <v>637</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>677</v>
+        <v>638</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>678</v>
+        <v>639</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>679</v>
+        <v>640</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>680</v>
+        <v>641</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>681</v>
+        <v>642</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>682</v>
+        <v>643</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>683</v>
+        <v>644</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>684</v>
+        <v>645</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>685</v>
+        <v>646</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>686</v>
+        <v>647</v>
       </c>
       <c r="R9" t="s">
-        <v>687</v>
+        <v>648</v>
       </c>
       <c r="S9" t="s">
-        <v>688</v>
+        <v>649</v>
       </c>
       <c r="T9" t="s">
-        <v>689</v>
+        <v>650</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>690</v>
+        <v>651</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>691</v>
+        <v>652</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>692</v>
+        <v>653</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>693</v>
+        <v>654</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>694</v>
+        <v>655</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>695</v>
+        <v>656</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>696</v>
+        <v>657</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>697</v>
+        <v>658</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>698</v>
+        <v>659</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>699</v>
+        <v>660</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>700</v>
+        <v>661</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>701</v>
+        <v>662</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>702</v>
+        <v>663</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>703</v>
+        <v>664</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>704</v>
+        <v>665</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>705</v>
+        <v>666</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>706</v>
+        <v>667</v>
       </c>
       <c r="R10" t="s">
-        <v>707</v>
+        <v>668</v>
       </c>
       <c r="S10" t="s">
-        <v>708</v>
+        <v>669</v>
       </c>
       <c r="T10" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>709</v>
+        <v>670</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>710</v>
+        <v>671</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>711</v>
+        <v>672</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>712</v>
+        <v>673</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>713</v>
+        <v>674</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>714</v>
+        <v>675</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>715</v>
+        <v>676</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>716</v>
+        <v>677</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>717</v>
+        <v>678</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>718</v>
+        <v>679</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>719</v>
+        <v>680</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>720</v>
+        <v>681</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>721</v>
+        <v>682</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>722</v>
+        <v>683</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>723</v>
+        <v>684</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>724</v>
+        <v>685</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>725</v>
+        <v>686</v>
       </c>
       <c r="R11" t="s">
-        <v>726</v>
+        <v>687</v>
       </c>
       <c r="S11" t="s">
-        <v>727</v>
+        <v>688</v>
       </c>
       <c r="T11" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>728</v>
+        <v>689</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>729</v>
+        <v>690</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>730</v>
+        <v>691</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>731</v>
+        <v>692</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>732</v>
+        <v>693</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>733</v>
+        <v>694</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>734</v>
+        <v>695</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>735</v>
+        <v>696</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>736</v>
+        <v>697</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>737</v>
+        <v>698</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>738</v>
+        <v>699</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>739</v>
+        <v>700</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>740</v>
+        <v>701</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>741</v>
+        <v>702</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>742</v>
+        <v>703</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>743</v>
+        <v>704</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>744</v>
+        <v>705</v>
       </c>
       <c r="R12" t="s">
-        <v>745</v>
+        <v>706</v>
       </c>
       <c r="S12" t="s">
-        <v>746</v>
+        <v>707</v>
       </c>
       <c r="T12" t="s">
-        <v>747</v>
+        <v>708</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>748</v>
+        <v>709</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>749</v>
+        <v>710</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>750</v>
+        <v>711</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>751</v>
+        <v>712</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>752</v>
+        <v>713</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>753</v>
+        <v>714</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>754</v>
+        <v>715</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>755</v>
+        <v>716</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>756</v>
+        <v>717</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>757</v>
+        <v>718</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>758</v>
+        <v>719</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>759</v>
+        <v>720</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>760</v>
+        <v>721</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>761</v>
+        <v>722</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>762</v>
+        <v>723</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>763</v>
+        <v>724</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>764</v>
+        <v>725</v>
       </c>
       <c r="R13" t="s">
-        <v>765</v>
+        <v>726</v>
       </c>
       <c r="S13" t="s">
-        <v>766</v>
+        <v>727</v>
       </c>
       <c r="T13" t="s">
-        <v>767</v>
+        <v>728</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>768</v>
+        <v>729</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>769</v>
+        <v>730</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>770</v>
+        <v>731</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>771</v>
+        <v>732</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>772</v>
+        <v>733</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>773</v>
+        <v>734</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>774</v>
+        <v>735</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>775</v>
+        <v>736</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>776</v>
+        <v>737</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>777</v>
+        <v>738</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>778</v>
+        <v>739</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>779</v>
+        <v>740</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>780</v>
+        <v>741</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>781</v>
+        <v>742</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>782</v>
+        <v>743</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>783</v>
+        <v>744</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>784</v>
+        <v>745</v>
       </c>
       <c r="R14" t="s">
-        <v>785</v>
+        <v>746</v>
       </c>
       <c r="S14" t="s">
-        <v>786</v>
+        <v>747</v>
       </c>
       <c r="T14" t="s">
-        <v>787</v>
+        <v>748</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>788</v>
+        <v>749</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>789</v>
+        <v>750</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>790</v>
+        <v>751</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>791</v>
+        <v>752</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>792</v>
+        <v>753</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>793</v>
+        <v>754</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>794</v>
+        <v>755</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>795</v>
+        <v>756</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>796</v>
+        <v>757</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>797</v>
+        <v>758</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>798</v>
+        <v>759</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>799</v>
+        <v>760</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>800</v>
+        <v>761</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>801</v>
+        <v>762</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>802</v>
+        <v>763</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>803</v>
+        <v>764</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>804</v>
+        <v>765</v>
       </c>
       <c r="R15" t="s">
-        <v>805</v>
+        <v>766</v>
       </c>
       <c r="S15" t="s">
-        <v>806</v>
+        <v>767</v>
       </c>
       <c r="T15" t="s">
-        <v>807</v>
+        <v>768</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>808</v>
+        <v>769</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>809</v>
+        <v>770</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>810</v>
+        <v>771</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>811</v>
+        <v>772</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>812</v>
+        <v>773</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>813</v>
+        <v>774</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>814</v>
+        <v>775</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>815</v>
+        <v>776</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>816</v>
+        <v>777</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>817</v>
+        <v>778</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>818</v>
+        <v>779</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>819</v>
+        <v>780</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>820</v>
+        <v>781</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>821</v>
+        <v>782</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>822</v>
+        <v>783</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>823</v>
+        <v>784</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>824</v>
+        <v>785</v>
       </c>
       <c r="R16" t="s">
-        <v>825</v>
+        <v>786</v>
       </c>
       <c r="S16" t="s">
-        <v>826</v>
+        <v>787</v>
       </c>
       <c r="T16" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>827</v>
+        <v>788</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>828</v>
+        <v>789</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>829</v>
+        <v>790</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>830</v>
+        <v>791</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>831</v>
+        <v>792</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>832</v>
+        <v>793</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>833</v>
+        <v>794</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>834</v>
+        <v>795</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>835</v>
+        <v>796</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>836</v>
+        <v>797</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>837</v>
+        <v>798</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>838</v>
+        <v>799</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>839</v>
+        <v>800</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>840</v>
+        <v>801</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>841</v>
+        <v>802</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>842</v>
+        <v>803</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>843</v>
+        <v>804</v>
       </c>
       <c r="R17" t="s">
-        <v>844</v>
+        <v>805</v>
       </c>
       <c r="S17" t="s">
-        <v>845</v>
+        <v>806</v>
       </c>
       <c r="T17" t="s">
-        <v>846</v>
+        <v>807</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>847</v>
+        <v>808</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>848</v>
+        <v>809</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>849</v>
+        <v>810</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>850</v>
+        <v>811</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>851</v>
+        <v>812</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>852</v>
+        <v>813</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>853</v>
+        <v>814</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>854</v>
+        <v>815</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>855</v>
+        <v>816</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>856</v>
+        <v>817</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>857</v>
+        <v>818</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>858</v>
+        <v>819</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>859</v>
+        <v>820</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>860</v>
+        <v>821</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>861</v>
+        <v>822</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>862</v>
+        <v>823</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>863</v>
+        <v>824</v>
       </c>
       <c r="R18" t="s">
-        <v>864</v>
+        <v>825</v>
       </c>
       <c r="S18" t="s">
-        <v>865</v>
+        <v>826</v>
       </c>
       <c r="T18" t="s">
-        <v>866</v>
+        <v>827</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>867</v>
+        <v>828</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>868</v>
+        <v>829</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>869</v>
+        <v>830</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>870</v>
+        <v>831</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>871</v>
+        <v>832</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>872</v>
+        <v>833</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>873</v>
+        <v>834</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>874</v>
+        <v>835</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>875</v>
+        <v>836</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>876</v>
+        <v>837</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>877</v>
+        <v>838</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>878</v>
+        <v>839</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>879</v>
+        <v>840</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>880</v>
+        <v>841</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>881</v>
+        <v>842</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>882</v>
+        <v>843</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>883</v>
+        <v>844</v>
       </c>
       <c r="R19" t="s">
-        <v>884</v>
+        <v>845</v>
       </c>
       <c r="S19" t="s">
-        <v>885</v>
+        <v>846</v>
       </c>
       <c r="T19" t="s">
-        <v>886</v>
+        <v>847</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>887</v>
+        <v>848</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>888</v>
+        <v>849</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>889</v>
+        <v>850</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>890</v>
+        <v>851</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>891</v>
+        <v>852</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>892</v>
+        <v>853</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>893</v>
+        <v>854</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>894</v>
+        <v>855</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>895</v>
+        <v>856</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>896</v>
+        <v>857</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>897</v>
+        <v>858</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>898</v>
+        <v>859</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>899</v>
+        <v>860</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>900</v>
+        <v>861</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>901</v>
+        <v>862</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>902</v>
+        <v>863</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>903</v>
+        <v>864</v>
       </c>
       <c r="R20" t="s">
-        <v>904</v>
+        <v>865</v>
       </c>
       <c r="S20" t="s">
-        <v>905</v>
+        <v>866</v>
       </c>
       <c r="T20" t="s">
-        <v>906</v>
+        <v>867</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>907</v>
+        <v>868</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>908</v>
+        <v>869</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>909</v>
+        <v>870</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>910</v>
+        <v>871</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>911</v>
+        <v>872</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>912</v>
+        <v>873</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>913</v>
+        <v>874</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>914</v>
+        <v>875</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>915</v>
+        <v>876</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>916</v>
+        <v>877</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>917</v>
+        <v>878</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>918</v>
+        <v>879</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>919</v>
+        <v>880</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>920</v>
+        <v>881</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>921</v>
+        <v>882</v>
       </c>
       <c r="P21" s="3" t="s">
-        <v>922</v>
+        <v>883</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>923</v>
+        <v>884</v>
       </c>
       <c r="R21" t="s">
-        <v>924</v>
+        <v>885</v>
       </c>
       <c r="S21" t="s">
-        <v>925</v>
+        <v>886</v>
       </c>
       <c r="T21" t="s">
-        <v>926</v>
+        <v>887</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>927</v>
+        <v>888</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>928</v>
+        <v>889</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>929</v>
+        <v>890</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>930</v>
+        <v>891</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>931</v>
+        <v>892</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>932</v>
+        <v>893</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>933</v>
+        <v>894</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>934</v>
+        <v>895</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>935</v>
+        <v>896</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>936</v>
+        <v>897</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>937</v>
+        <v>898</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>938</v>
+        <v>899</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>939</v>
+        <v>900</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>940</v>
+        <v>901</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>941</v>
+        <v>902</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>942</v>
+        <v>903</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>943</v>
+        <v>904</v>
       </c>
       <c r="R22" t="s">
-        <v>944</v>
+        <v>905</v>
       </c>
       <c r="S22" t="s">
-        <v>945</v>
+        <v>906</v>
       </c>
       <c r="T22" t="s">
-        <v>946</v>
+        <v>907</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>947</v>
+        <v>908</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>948</v>
+        <v>909</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>949</v>
+        <v>910</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>950</v>
+        <v>911</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>951</v>
+        <v>912</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>952</v>
+        <v>913</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>953</v>
+        <v>914</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>954</v>
+        <v>915</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>955</v>
+        <v>916</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>956</v>
+        <v>917</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>957</v>
+        <v>918</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>958</v>
+        <v>919</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>959</v>
+        <v>920</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>960</v>
+        <v>921</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>961</v>
+        <v>922</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>962</v>
+        <v>923</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>963</v>
+        <v>924</v>
       </c>
       <c r="R23" t="s">
-        <v>964</v>
+        <v>925</v>
       </c>
       <c r="S23" t="s">
-        <v>965</v>
+        <v>926</v>
       </c>
       <c r="T23" t="s">
-        <v>966</v>
+        <v>927</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>967</v>
+        <v>928</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>968</v>
+        <v>929</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>969</v>
+        <v>930</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>970</v>
+        <v>931</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>971</v>
+        <v>932</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>972</v>
+        <v>933</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>973</v>
+        <v>934</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>974</v>
+        <v>935</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>975</v>
+        <v>936</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>976</v>
+        <v>937</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>977</v>
+        <v>938</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>978</v>
+        <v>939</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>979</v>
+        <v>940</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>980</v>
+        <v>941</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>981</v>
+        <v>942</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>982</v>
+        <v>943</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>983</v>
+        <v>944</v>
       </c>
       <c r="R24" t="s">
-        <v>984</v>
+        <v>945</v>
       </c>
       <c r="S24" t="s">
-        <v>985</v>
+        <v>946</v>
       </c>
       <c r="T24" t="s">
-        <v>986</v>
+        <v>947</v>
       </c>
     </row>
   </sheetData>
@@ -8314,1416 +8317,1416 @@
         <v>23</v>
       </c>
       <c r="E2" s="9" t="s">
+        <v>1191</v>
+      </c>
+      <c r="F2" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="G2" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="9" t="s">
-        <v>26</v>
-      </c>
       <c r="H2" s="9" t="s">
+        <v>1174</v>
+      </c>
+      <c r="I2" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="J2" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="K2" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="L2" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="M2" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="M2" s="9" t="s">
+      <c r="N2" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="N2" s="9" t="s">
+      <c r="O2" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="9" t="s">
+      <c r="P2" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="P2" s="9" t="s">
+      <c r="Q2" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="Q2" s="9" t="s">
+      <c r="R2" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="R2" s="10" t="s">
+      <c r="S2" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="S2" s="10" t="s">
+      <c r="T2" s="10" t="s">
         <v>38</v>
-      </c>
-      <c r="T2" s="10" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="C3" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="D3" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="E3" s="9" t="s">
+        <v>1192</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E3" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="H3" s="9" t="s">
+      <c r="I3" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="J3" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="K3" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="L3" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="M3" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="M3" s="9" t="s">
+      <c r="N3" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="O3" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="O3" s="9" t="s">
+      <c r="P3" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="P3" s="9" t="s">
+      <c r="Q3" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q3" s="9" t="s">
+      <c r="R3" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="R3" s="10" t="s">
+      <c r="S3" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="S3" s="10" t="s">
+      <c r="T3" s="10" t="s">
         <v>58</v>
-      </c>
-      <c r="T3" s="10" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="C4" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="D4" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="E4" s="9" t="s">
+        <v>1193</v>
+      </c>
+      <c r="F4" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="G4" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="H4" s="9" t="s">
+        <v>1175</v>
+      </c>
+      <c r="I4" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="J4" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="K4" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="L4" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="M4" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="N4" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="L4" s="9" t="s">
+      <c r="O4" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="M4" s="9" t="s">
+      <c r="P4" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="N4" s="9" t="s">
+      <c r="Q4" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="O4" s="9" t="s">
+      <c r="R4" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="P4" s="9" t="s">
+      <c r="S4" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="Q4" s="9" t="s">
+      <c r="T4" s="10" t="s">
         <v>76</v>
-      </c>
-      <c r="R4" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="S4" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="T4" s="10" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="E5" s="9" t="s">
+        <v>1194</v>
+      </c>
+      <c r="F5" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="G5" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="D5" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="E5" s="9" t="s">
+      <c r="H5" s="9" t="s">
+        <v>1176</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>1173</v>
+      </c>
+      <c r="J5" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="K5" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="L5" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="M5" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="I5" s="9" t="s">
-        <v>1212</v>
-      </c>
-      <c r="J5" s="9" t="s">
+      <c r="N5" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="K5" s="9" t="s">
+      <c r="O5" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="L5" s="9" t="s">
+      <c r="P5" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="M5" s="9" t="s">
+      <c r="Q5" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="N5" s="9" t="s">
+      <c r="R5" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="O5" s="9" t="s">
+      <c r="S5" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="P5" s="9" t="s">
+      <c r="T5" s="10" t="s">
         <v>94</v>
-      </c>
-      <c r="Q5" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="R5" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="S5" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="T5" s="10" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F6" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="G6" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="H6" s="9" t="s">
+        <v>1177</v>
+      </c>
+      <c r="I6" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="J6" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="K6" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="L6" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="M6" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="N6" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="O6" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="P6" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="Q6" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="L6" s="9" t="s">
+      <c r="R6" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="M6" s="9" t="s">
+      <c r="S6" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="N6" s="9" t="s">
+      <c r="T6" s="10" t="s">
         <v>112</v>
-      </c>
-      <c r="O6" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="P6" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q6" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="R6" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="S6" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="T6" s="10" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>1196</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>1178</v>
+      </c>
+      <c r="I7" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="J7" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="K7" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="L7" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="M7" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="N7" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="O7" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="P7" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="Q7" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="J7" s="9" t="s">
+      <c r="R7" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="K7" s="9" t="s">
+      <c r="S7" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="L7" s="9" t="s">
+      <c r="T7" s="10" t="s">
         <v>130</v>
-      </c>
-      <c r="M7" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="N7" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="O7" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="P7" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q7" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="R7" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="S7" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="T7" s="10" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>1197</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>1179</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="K8" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="L8" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="M8" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="N8" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="O8" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="P8" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="Q8" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="R8" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="S8" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="J8" s="9" t="s">
+      <c r="T8" s="10" t="s">
         <v>148</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="L8" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="M8" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="N8" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="O8" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="P8" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q8" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="R8" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="S8" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="T8" s="10" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>1198</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>1180</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="M9" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="N9" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="O9" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="P9" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="Q9" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="R9" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="S9" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="T9" s="10" t="s">
         <v>166</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="M9" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="N9" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="O9" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="P9" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="Q9" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="R9" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="S9" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="T9" s="10" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>1199</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>1181</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="M10" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="N10" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="O10" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="P10" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="Q10" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="R10" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="S10" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="T10" s="10" t="s">
         <v>185</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="K10" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="L10" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="M10" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="N10" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="O10" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="P10" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q10" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="R10" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="S10" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="T10" s="10" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>1200</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>1182</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="N11" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="O11" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="P11" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="Q11" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="R11" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="S11" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="T11" s="10" t="s">
         <v>203</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="K11" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="M11" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="N11" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="O11" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="P11" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="Q11" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="R11" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="S11" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="T11" s="10" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>1183</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="M12" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="N12" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="O12" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="P12" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q12" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="R12" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="S12" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="T12" s="10" t="s">
         <v>221</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>223</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>225</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="J12" s="9" t="s">
-        <v>228</v>
-      </c>
-      <c r="K12" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="L12" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="M12" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="N12" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="O12" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="P12" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="Q12" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="R12" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="S12" s="10" t="s">
-        <v>237</v>
-      </c>
-      <c r="T12" s="10" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>1202</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>1184</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="M13" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="O13" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="P13" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q13" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="R13" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="S13" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="T13" s="10" t="s">
         <v>240</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="K13" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="L13" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="M13" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="N13" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="O13" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="P13" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="Q13" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="R13" s="10" t="s">
-        <v>256</v>
-      </c>
-      <c r="S13" s="10" t="s">
-        <v>257</v>
-      </c>
-      <c r="T13" s="10" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>262</v>
+        <v>244</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>263</v>
+        <v>1203</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>264</v>
+        <v>245</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>265</v>
+        <v>246</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>266</v>
+        <v>1185</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>268</v>
+        <v>248</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>269</v>
+        <v>249</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="M14" s="9" t="s">
-        <v>271</v>
+        <v>251</v>
       </c>
       <c r="N14" s="9" t="s">
-        <v>272</v>
+        <v>252</v>
       </c>
       <c r="O14" s="9" t="s">
-        <v>273</v>
+        <v>253</v>
       </c>
       <c r="P14" s="9" t="s">
-        <v>274</v>
+        <v>254</v>
       </c>
       <c r="Q14" s="9" t="s">
-        <v>275</v>
+        <v>255</v>
       </c>
       <c r="R14" s="10" t="s">
-        <v>276</v>
+        <v>256</v>
       </c>
       <c r="S14" s="10" t="s">
-        <v>277</v>
+        <v>257</v>
       </c>
       <c r="T14" s="10" t="s">
-        <v>278</v>
+        <v>258</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
-        <v>279</v>
+        <v>259</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>282</v>
+        <v>262</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>283</v>
+        <v>1204</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>284</v>
+        <v>263</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>285</v>
+        <v>264</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>286</v>
+        <v>1186</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>288</v>
+        <v>266</v>
       </c>
       <c r="K15" s="9" t="s">
-        <v>289</v>
+        <v>267</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="M15" s="9" t="s">
-        <v>291</v>
+        <v>269</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>292</v>
+        <v>270</v>
       </c>
       <c r="O15" s="9" t="s">
-        <v>293</v>
+        <v>271</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>294</v>
+        <v>272</v>
       </c>
       <c r="Q15" s="9" t="s">
-        <v>295</v>
+        <v>273</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>296</v>
+        <v>274</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>297</v>
+        <v>275</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>298</v>
+        <v>276</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>301</v>
+        <v>279</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>302</v>
+        <v>280</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>303</v>
+        <v>1205</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>304</v>
+        <v>281</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>305</v>
+        <v>282</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>306</v>
+        <v>26</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>307</v>
+        <v>283</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="K16" s="9" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="L16" s="9" t="s">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="M16" s="9" t="s">
-        <v>311</v>
+        <v>287</v>
       </c>
       <c r="N16" s="9" t="s">
-        <v>312</v>
+        <v>288</v>
       </c>
       <c r="O16" s="9" t="s">
-        <v>313</v>
+        <v>289</v>
       </c>
       <c r="P16" s="9" t="s">
-        <v>314</v>
+        <v>290</v>
       </c>
       <c r="Q16" s="9" t="s">
-        <v>315</v>
+        <v>291</v>
       </c>
       <c r="R16" s="10" t="s">
-        <v>316</v>
+        <v>292</v>
       </c>
       <c r="S16" s="10" t="s">
-        <v>317</v>
+        <v>293</v>
       </c>
       <c r="T16" s="10" t="s">
-        <v>318</v>
+        <v>294</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
-        <v>319</v>
+        <v>295</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>320</v>
+        <v>296</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>321</v>
+        <v>297</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>322</v>
+        <v>298</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>323</v>
+        <v>1206</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>324</v>
+        <v>299</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>326</v>
+        <v>1187</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>327</v>
+        <v>302</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>328</v>
+        <v>303</v>
       </c>
       <c r="K17" s="9" t="s">
-        <v>329</v>
+        <v>304</v>
       </c>
       <c r="L17" s="9" t="s">
-        <v>330</v>
+        <v>305</v>
       </c>
       <c r="M17" s="9" t="s">
-        <v>331</v>
+        <v>306</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>332</v>
+        <v>307</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>333</v>
+        <v>308</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>334</v>
+        <v>309</v>
       </c>
       <c r="Q17" s="9" t="s">
-        <v>335</v>
+        <v>310</v>
       </c>
       <c r="R17" s="10" t="s">
-        <v>336</v>
+        <v>311</v>
       </c>
       <c r="S17" s="10" t="s">
-        <v>337</v>
+        <v>312</v>
       </c>
       <c r="T17" s="10" t="s">
-        <v>338</v>
+        <v>313</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
-        <v>339</v>
+        <v>314</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>340</v>
+        <v>315</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>341</v>
+        <v>316</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>342</v>
+        <v>317</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>343</v>
+        <v>1207</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>344</v>
+        <v>318</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>345</v>
+        <v>319</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>346</v>
+        <v>228</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>347</v>
+        <v>320</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>348</v>
+        <v>321</v>
       </c>
       <c r="K18" s="9" t="s">
-        <v>349</v>
+        <v>322</v>
       </c>
       <c r="L18" s="9" t="s">
-        <v>350</v>
+        <v>323</v>
       </c>
       <c r="M18" s="9" t="s">
-        <v>351</v>
+        <v>324</v>
       </c>
       <c r="N18" s="9" t="s">
-        <v>352</v>
+        <v>325</v>
       </c>
       <c r="O18" s="9" t="s">
-        <v>353</v>
+        <v>326</v>
       </c>
       <c r="P18" s="9" t="s">
-        <v>354</v>
+        <v>327</v>
       </c>
       <c r="Q18" s="9" t="s">
-        <v>355</v>
+        <v>328</v>
       </c>
       <c r="R18" s="10" t="s">
-        <v>356</v>
+        <v>329</v>
       </c>
       <c r="S18" s="10" t="s">
-        <v>357</v>
+        <v>330</v>
       </c>
       <c r="T18" s="10" t="s">
-        <v>358</v>
+        <v>331</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
-        <v>359</v>
+        <v>332</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>360</v>
+        <v>333</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>361</v>
+        <v>334</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>362</v>
+        <v>335</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>363</v>
+        <v>1208</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>364</v>
+        <v>336</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>365</v>
+        <v>337</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>366</v>
+        <v>1188</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>367</v>
+        <v>338</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>368</v>
+        <v>339</v>
       </c>
       <c r="K19" s="9" t="s">
-        <v>369</v>
+        <v>340</v>
       </c>
       <c r="L19" s="9" t="s">
-        <v>370</v>
+        <v>341</v>
       </c>
       <c r="M19" s="9" t="s">
-        <v>371</v>
+        <v>342</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>372</v>
+        <v>343</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>373</v>
+        <v>344</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>374</v>
+        <v>345</v>
       </c>
       <c r="Q19" s="9" t="s">
-        <v>375</v>
+        <v>346</v>
       </c>
       <c r="R19" s="10" t="s">
-        <v>376</v>
+        <v>347</v>
       </c>
       <c r="S19" s="10" t="s">
-        <v>377</v>
+        <v>348</v>
       </c>
       <c r="T19" s="10" t="s">
-        <v>378</v>
+        <v>349</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
-        <v>379</v>
+        <v>350</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>380</v>
+        <v>351</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>381</v>
+        <v>352</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>382</v>
+        <v>353</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>383</v>
+        <v>1212</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>384</v>
+        <v>354</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>385</v>
+        <v>355</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>386</v>
+        <v>83</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>387</v>
+        <v>356</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="K20" s="9" t="s">
-        <v>389</v>
+        <v>358</v>
       </c>
       <c r="L20" s="9" t="s">
-        <v>390</v>
+        <v>359</v>
       </c>
       <c r="M20" s="9" t="s">
-        <v>391</v>
+        <v>360</v>
       </c>
       <c r="N20" s="9" t="s">
-        <v>392</v>
+        <v>361</v>
       </c>
       <c r="O20" s="10" t="s">
-        <v>393</v>
+        <v>362</v>
       </c>
       <c r="P20" s="9" t="s">
-        <v>394</v>
+        <v>363</v>
       </c>
       <c r="Q20" s="9" t="s">
-        <v>395</v>
+        <v>364</v>
       </c>
       <c r="R20" s="10" t="s">
-        <v>396</v>
+        <v>365</v>
       </c>
       <c r="S20" s="10" t="s">
-        <v>397</v>
+        <v>366</v>
       </c>
       <c r="T20" s="10" t="s">
-        <v>398</v>
+        <v>367</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
-        <v>399</v>
+        <v>368</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>400</v>
+        <v>369</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>401</v>
+        <v>370</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>402</v>
+        <v>371</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>403</v>
+        <v>1213</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>404</v>
+        <v>372</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>405</v>
+        <v>373</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>406</v>
+        <v>301</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>407</v>
+        <v>374</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>408</v>
+        <v>375</v>
       </c>
       <c r="K21" s="9" t="s">
-        <v>409</v>
+        <v>376</v>
       </c>
       <c r="L21" s="9" t="s">
-        <v>410</v>
+        <v>377</v>
       </c>
       <c r="M21" s="9" t="s">
-        <v>411</v>
+        <v>378</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>412</v>
+        <v>379</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>413</v>
+        <v>380</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>414</v>
+        <v>381</v>
       </c>
       <c r="Q21" s="9" t="s">
-        <v>415</v>
+        <v>382</v>
       </c>
       <c r="R21" s="10" t="s">
-        <v>416</v>
+        <v>383</v>
       </c>
       <c r="S21" s="10" t="s">
-        <v>417</v>
+        <v>384</v>
       </c>
       <c r="T21" s="10" t="s">
-        <v>418</v>
+        <v>385</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
-        <v>419</v>
+        <v>386</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>420</v>
+        <v>387</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>421</v>
+        <v>388</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>422</v>
+        <v>389</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>423</v>
+        <v>1209</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>424</v>
+        <v>390</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>425</v>
+        <v>391</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>426</v>
+        <v>46</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>427</v>
+        <v>392</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>428</v>
+        <v>393</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>429</v>
+        <v>394</v>
       </c>
       <c r="L22" s="9" t="s">
-        <v>430</v>
+        <v>395</v>
       </c>
       <c r="M22" s="9" t="s">
-        <v>431</v>
+        <v>396</v>
       </c>
       <c r="N22" s="9" t="s">
-        <v>432</v>
+        <v>397</v>
       </c>
       <c r="O22" s="9" t="s">
-        <v>433</v>
+        <v>398</v>
       </c>
       <c r="P22" s="9" t="s">
-        <v>434</v>
+        <v>399</v>
       </c>
       <c r="Q22" s="9" t="s">
-        <v>435</v>
+        <v>400</v>
       </c>
       <c r="R22" s="10" t="s">
-        <v>436</v>
+        <v>401</v>
       </c>
       <c r="S22" s="10" t="s">
-        <v>437</v>
+        <v>402</v>
       </c>
       <c r="T22" s="10" t="s">
-        <v>438</v>
+        <v>403</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
-        <v>439</v>
+        <v>404</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>440</v>
+        <v>405</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>441</v>
+        <v>406</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>442</v>
+        <v>407</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>443</v>
+        <v>1210</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>444</v>
+        <v>408</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>445</v>
+        <v>409</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>446</v>
+        <v>1189</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>447</v>
+        <v>410</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>448</v>
+        <v>411</v>
       </c>
       <c r="K23" s="9" t="s">
-        <v>449</v>
+        <v>412</v>
       </c>
       <c r="L23" s="9" t="s">
-        <v>450</v>
+        <v>413</v>
       </c>
       <c r="M23" s="9" t="s">
-        <v>451</v>
+        <v>414</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>452</v>
+        <v>415</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>453</v>
+        <v>416</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>454</v>
+        <v>417</v>
       </c>
       <c r="Q23" s="9" t="s">
-        <v>455</v>
+        <v>418</v>
       </c>
       <c r="R23" s="10" t="s">
-        <v>456</v>
+        <v>419</v>
       </c>
       <c r="S23" s="10" t="s">
-        <v>457</v>
+        <v>420</v>
       </c>
       <c r="T23" s="10" t="s">
-        <v>458</v>
+        <v>421</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
-        <v>459</v>
+        <v>422</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>460</v>
+        <v>423</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>461</v>
+        <v>424</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>462</v>
+        <v>425</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>463</v>
+        <v>1211</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>464</v>
+        <v>426</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>465</v>
+        <v>427</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>466</v>
+        <v>1190</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>467</v>
+        <v>428</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>468</v>
+        <v>429</v>
       </c>
       <c r="K24" s="9" t="s">
-        <v>469</v>
+        <v>430</v>
       </c>
       <c r="L24" s="9" t="s">
-        <v>470</v>
+        <v>431</v>
       </c>
       <c r="M24" s="9" t="s">
-        <v>471</v>
+        <v>432</v>
       </c>
       <c r="N24" s="9" t="s">
-        <v>472</v>
+        <v>433</v>
       </c>
       <c r="O24" s="9" t="s">
-        <v>473</v>
+        <v>434</v>
       </c>
       <c r="P24" s="9" t="s">
-        <v>474</v>
+        <v>435</v>
       </c>
       <c r="Q24" s="9" t="s">
-        <v>475</v>
+        <v>436</v>
       </c>
       <c r="R24" s="10" t="s">
-        <v>476</v>
+        <v>437</v>
       </c>
       <c r="S24" s="10" t="s">
-        <v>477</v>
+        <v>438</v>
       </c>
       <c r="T24" s="10" t="s">
-        <v>478</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -9747,28 +9750,28 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>479</v>
+        <v>440</v>
       </c>
       <c r="B1" t="s">
-        <v>987</v>
+        <v>948</v>
       </c>
       <c r="C1" t="s">
-        <v>988</v>
+        <v>949</v>
       </c>
       <c r="D1" t="s">
-        <v>989</v>
+        <v>950</v>
       </c>
       <c r="E1" t="s">
-        <v>990</v>
+        <v>951</v>
       </c>
       <c r="F1" t="s">
-        <v>991</v>
+        <v>952</v>
       </c>
       <c r="G1" t="s">
-        <v>992</v>
+        <v>953</v>
       </c>
       <c r="H1" t="s">
-        <v>993</v>
+        <v>954</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -9776,13 +9779,13 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>994</v>
+        <v>955</v>
       </c>
       <c r="C2" t="s">
-        <v>995</v>
+        <v>956</v>
       </c>
       <c r="D2" t="s">
-        <v>996</v>
+        <v>957</v>
       </c>
       <c r="E2">
         <v>100000000</v>
@@ -9791,10 +9794,10 @@
         <v>2575000000</v>
       </c>
       <c r="G2" t="s">
-        <v>997</v>
+        <v>958</v>
       </c>
       <c r="H2" t="s">
-        <v>998</v>
+        <v>959</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -9802,13 +9805,13 @@
         <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>999</v>
+        <v>960</v>
       </c>
       <c r="C3" t="s">
-        <v>1000</v>
+        <v>961</v>
       </c>
       <c r="D3" t="s">
-        <v>1001</v>
+        <v>962</v>
       </c>
       <c r="E3">
         <v>100000000</v>
@@ -9817,10 +9820,10 @@
         <v>211000000</v>
       </c>
       <c r="G3" t="s">
-        <v>1002</v>
+        <v>963</v>
       </c>
       <c r="H3" t="s">
-        <v>1003</v>
+        <v>964</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -9831,10 +9834,10 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>1004</v>
+        <v>965</v>
       </c>
       <c r="D4" t="s">
-        <v>1005</v>
+        <v>966</v>
       </c>
       <c r="E4">
         <v>100000000</v>
@@ -9843,10 +9846,10 @@
         <v>810000000</v>
       </c>
       <c r="G4" t="s">
-        <v>1006</v>
+        <v>967</v>
       </c>
       <c r="H4" t="s">
-        <v>1007</v>
+        <v>968</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -9854,13 +9857,13 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>1008</v>
+        <v>969</v>
       </c>
       <c r="C5" t="s">
-        <v>1009</v>
+        <v>970</v>
       </c>
       <c r="D5" t="s">
-        <v>1010</v>
+        <v>971</v>
       </c>
       <c r="E5">
         <v>100000000</v>
@@ -9869,10 +9872,10 @@
         <v>2569000000</v>
       </c>
       <c r="G5" t="s">
-        <v>1011</v>
+        <v>972</v>
       </c>
       <c r="H5" t="s">
-        <v>1012</v>
+        <v>973</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -9880,13 +9883,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>1013</v>
+        <v>974</v>
       </c>
       <c r="C6" t="s">
-        <v>1014</v>
+        <v>975</v>
       </c>
       <c r="D6" t="s">
-        <v>1015</v>
+        <v>976</v>
       </c>
       <c r="E6">
         <v>100000000</v>
@@ -9895,10 +9898,10 @@
         <v>759000000</v>
       </c>
       <c r="G6" t="s">
-        <v>1016</v>
+        <v>977</v>
       </c>
       <c r="H6" t="s">
-        <v>1017</v>
+        <v>978</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -9906,13 +9909,13 @@
         <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>1018</v>
+        <v>979</v>
       </c>
       <c r="C7" t="s">
-        <v>1019</v>
+        <v>980</v>
       </c>
       <c r="D7" t="s">
-        <v>1020</v>
+        <v>981</v>
       </c>
       <c r="E7">
         <v>100000000</v>
@@ -9921,10 +9924,10 @@
         <v>280000000</v>
       </c>
       <c r="G7" t="s">
-        <v>1021</v>
+        <v>982</v>
       </c>
       <c r="H7" t="s">
-        <v>1022</v>
+        <v>983</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -9932,13 +9935,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>1023</v>
+        <v>984</v>
       </c>
       <c r="C8" t="s">
-        <v>1024</v>
+        <v>985</v>
       </c>
       <c r="D8" t="s">
-        <v>1025</v>
+        <v>986</v>
       </c>
       <c r="E8">
         <v>100000000</v>
@@ -9947,10 +9950,10 @@
         <v>2154000000</v>
       </c>
       <c r="G8" t="s">
-        <v>1026</v>
+        <v>987</v>
       </c>
       <c r="H8" t="s">
-        <v>1027</v>
+        <v>988</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -9958,13 +9961,13 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>1028</v>
+        <v>989</v>
       </c>
       <c r="C9" t="s">
-        <v>1029</v>
+        <v>990</v>
       </c>
       <c r="D9" t="s">
-        <v>1030</v>
+        <v>991</v>
       </c>
       <c r="E9">
         <v>100000000</v>
@@ -9973,10 +9976,10 @@
         <v>223000000</v>
       </c>
       <c r="G9" t="s">
-        <v>1031</v>
+        <v>992</v>
       </c>
       <c r="H9" t="s">
-        <v>1032</v>
+        <v>993</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
@@ -9984,13 +9987,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>1033</v>
+        <v>994</v>
       </c>
       <c r="C10" t="s">
-        <v>1034</v>
+        <v>995</v>
       </c>
       <c r="D10" t="s">
-        <v>1035</v>
+        <v>996</v>
       </c>
       <c r="E10">
         <v>100000000</v>
@@ -9999,10 +10002,10 @@
         <v>11000000</v>
       </c>
       <c r="G10" t="s">
-        <v>1036</v>
+        <v>997</v>
       </c>
       <c r="H10" t="s">
-        <v>1037</v>
+        <v>998</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
@@ -10010,13 +10013,13 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>1038</v>
+        <v>999</v>
       </c>
       <c r="C11" t="s">
-        <v>1039</v>
+        <v>1000</v>
       </c>
       <c r="D11" t="s">
-        <v>1040</v>
+        <v>1001</v>
       </c>
       <c r="E11">
         <v>100000000</v>
@@ -10025,10 +10028,10 @@
         <v>119000000</v>
       </c>
       <c r="G11" t="s">
-        <v>1041</v>
+        <v>1002</v>
       </c>
       <c r="H11" t="s">
-        <v>1042</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
@@ -10036,13 +10039,13 @@
         <v>0</v>
       </c>
       <c r="B12" t="s">
-        <v>1043</v>
+        <v>1004</v>
       </c>
       <c r="C12" t="s">
-        <v>1044</v>
+        <v>1005</v>
       </c>
       <c r="D12" t="s">
-        <v>1045</v>
+        <v>1006</v>
       </c>
       <c r="E12">
         <v>100000000</v>
@@ -10051,24 +10054,24 @@
         <v>2121000000</v>
       </c>
       <c r="G12" t="s">
-        <v>1046</v>
+        <v>1007</v>
       </c>
       <c r="H12" t="s">
-        <v>1047</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>523</v>
+        <v>484</v>
       </c>
       <c r="B13" t="s">
-        <v>1048</v>
+        <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>1049</v>
+        <v>1010</v>
       </c>
       <c r="D13" t="s">
-        <v>1050</v>
+        <v>1011</v>
       </c>
       <c r="E13">
         <v>100000000</v>
@@ -10077,10 +10080,10 @@
         <v>300000000</v>
       </c>
       <c r="G13" t="s">
-        <v>1051</v>
+        <v>1012</v>
       </c>
       <c r="H13" t="s">
-        <v>1052</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
@@ -10088,13 +10091,13 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>1053</v>
+        <v>1014</v>
       </c>
       <c r="C14" t="s">
-        <v>1054</v>
+        <v>1015</v>
       </c>
       <c r="D14" t="s">
-        <v>1055</v>
+        <v>1016</v>
       </c>
       <c r="E14">
         <v>100000000</v>
@@ -10103,10 +10106,10 @@
         <v>357000000</v>
       </c>
       <c r="G14" t="s">
-        <v>1056</v>
+        <v>1017</v>
       </c>
       <c r="H14" t="s">
-        <v>1057</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
@@ -10114,13 +10117,13 @@
         <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>1058</v>
+        <v>1019</v>
       </c>
       <c r="C15" t="s">
-        <v>1059</v>
+        <v>1020</v>
       </c>
       <c r="D15" t="s">
-        <v>1060</v>
+        <v>1021</v>
       </c>
       <c r="E15">
         <v>100000000</v>
@@ -10129,24 +10132,24 @@
         <v>137000000</v>
       </c>
       <c r="G15" t="s">
-        <v>1061</v>
+        <v>1022</v>
       </c>
       <c r="H15" t="s">
-        <v>1062</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>513</v>
+        <v>474</v>
       </c>
       <c r="B16" t="s">
-        <v>1063</v>
+        <v>1024</v>
       </c>
       <c r="C16" t="s">
-        <v>1044</v>
+        <v>1005</v>
       </c>
       <c r="D16" t="s">
-        <v>1064</v>
+        <v>1025</v>
       </c>
       <c r="E16">
         <v>100000000</v>
@@ -10155,10 +10158,10 @@
         <v>440000000</v>
       </c>
       <c r="G16" t="s">
-        <v>1065</v>
+        <v>1026</v>
       </c>
       <c r="H16" t="s">
-        <v>1066</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
@@ -10166,13 +10169,13 @@
         <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>1067</v>
+        <v>1028</v>
       </c>
       <c r="C17" t="s">
-        <v>1068</v>
+        <v>1029</v>
       </c>
       <c r="D17" t="s">
-        <v>1069</v>
+        <v>1030</v>
       </c>
       <c r="E17">
         <v>100000000</v>
@@ -10181,10 +10184,10 @@
         <v>181000000</v>
       </c>
       <c r="G17" t="s">
-        <v>1070</v>
+        <v>1031</v>
       </c>
       <c r="H17" t="s">
-        <v>1071</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
@@ -10192,13 +10195,13 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>1072</v>
+        <v>1033</v>
       </c>
       <c r="C18" t="s">
-        <v>1073</v>
+        <v>1034</v>
       </c>
       <c r="D18" t="s">
-        <v>1074</v>
+        <v>1035</v>
       </c>
       <c r="E18">
         <v>100000000</v>
@@ -10207,36 +10210,36 @@
         <v>210000000</v>
       </c>
       <c r="G18" t="s">
-        <v>1075</v>
+        <v>1036</v>
       </c>
       <c r="H18" t="s">
-        <v>1076</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>1077</v>
+        <v>1038</v>
       </c>
       <c r="B19" t="s">
-        <v>1078</v>
+        <v>1039</v>
       </c>
       <c r="C19" t="s">
-        <v>1079</v>
+        <v>1040</v>
       </c>
       <c r="D19" t="s">
-        <v>1080</v>
+        <v>1041</v>
       </c>
       <c r="E19" t="s">
-        <v>1081</v>
+        <v>1042</v>
       </c>
       <c r="F19" t="s">
-        <v>1081</v>
+        <v>1042</v>
       </c>
       <c r="G19" t="s">
-        <v>1082</v>
+        <v>1043</v>
       </c>
       <c r="H19" t="s">
-        <v>1083</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
@@ -10244,51 +10247,51 @@
         <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>1084</v>
+        <v>1045</v>
       </c>
       <c r="C20" t="s">
-        <v>1085</v>
+        <v>1046</v>
       </c>
       <c r="D20" t="s">
-        <v>1086</v>
+        <v>1047</v>
       </c>
       <c r="E20" t="s">
-        <v>1081</v>
+        <v>1042</v>
       </c>
       <c r="F20" t="s">
-        <v>1081</v>
+        <v>1042</v>
       </c>
       <c r="G20" t="s">
-        <v>1087</v>
+        <v>1048</v>
       </c>
       <c r="H20" t="s">
-        <v>1088</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>1089</v>
+        <v>1050</v>
       </c>
       <c r="B21" t="s">
-        <v>1090</v>
+        <v>1051</v>
       </c>
       <c r="C21" t="s">
-        <v>1091</v>
+        <v>1052</v>
       </c>
       <c r="D21" t="s">
-        <v>1092</v>
+        <v>1053</v>
       </c>
       <c r="E21" t="s">
-        <v>1081</v>
+        <v>1042</v>
       </c>
       <c r="F21" t="s">
-        <v>1081</v>
+        <v>1042</v>
       </c>
       <c r="G21" t="s">
-        <v>1093</v>
+        <v>1054</v>
       </c>
       <c r="H21" t="s">
-        <v>1094</v>
+        <v>1055</v>
       </c>
     </row>
   </sheetData>
